--- a/apartments.xlsx
+++ b/apartments.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LOQ\Documents\GitHub\Apartment-Recommendation-Chatbot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{D6C5516A-F337-4C2B-8307-EB7C371A3EB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F9FC2DAE-282F-4F4F-85F4-98D313DF2EC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{85F7AF4C-DA42-4951-85AB-D96CBB4AA5DE}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{637C1A01-FA05-4636-AD4C-D533005E20C1}"/>
   </bookViews>
   <sheets>
     <sheet name="apartments" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="226">
   <si>
     <t>apartment_id</t>
   </si>
@@ -28,6 +28,12 @@
     <t>title</t>
   </si>
   <si>
+    <t>city</t>
+  </si>
+  <si>
+    <t>area</t>
+  </si>
+  <si>
     <t>location</t>
   </si>
   <si>
@@ -61,6 +67,12 @@
     <t>apartment</t>
   </si>
   <si>
+    <t xml:space="preserve"> New Cairo</t>
+  </si>
+  <si>
+    <t>Moon Residences, Fifth Square, Fifth Settlement</t>
+  </si>
+  <si>
     <t>Moon Residences, Fifth Square, Fifth Settlement, New Cairo</t>
   </si>
   <si>
@@ -82,6 +94,9 @@
     <t>studio</t>
   </si>
   <si>
+    <t>Palm Hills New Cairo, Fifth Settlement</t>
+  </si>
+  <si>
     <t>Palm Hills New Cairo, Fifth Settlement, New Cairo</t>
   </si>
   <si>
@@ -97,6 +112,9 @@
     <t>AP003</t>
   </si>
   <si>
+    <t>The Address East, 90 Street</t>
+  </si>
+  <si>
     <t>The Address East, 90 Street, New Cairo</t>
   </si>
   <si>
@@ -112,6 +130,12 @@
     <t>AP004</t>
   </si>
   <si>
+    <t xml:space="preserve"> East Cairo</t>
+  </si>
+  <si>
+    <t>East Vale, Mostakbal City</t>
+  </si>
+  <si>
     <t>East Vale, Mostakbal City, East Cairo</t>
   </si>
   <si>
@@ -127,6 +151,12 @@
     <t>AP005</t>
   </si>
   <si>
+    <t xml:space="preserve"> Madinaty</t>
+  </si>
+  <si>
+    <t>Privado, Madinaty B15</t>
+  </si>
+  <si>
     <t>Privado, Madinaty B15, Madinaty</t>
   </si>
   <si>
@@ -142,6 +172,9 @@
     <t>AP006</t>
   </si>
   <si>
+    <t>Mostashareen, North Investors Area</t>
+  </si>
+  <si>
     <t>Mostashareen, North Investors Area, New Cairo</t>
   </si>
   <si>
@@ -157,6 +190,9 @@
     <t>AP007</t>
   </si>
   <si>
+    <t>Jiwar Compound, 6th Settlement</t>
+  </si>
+  <si>
     <t>Jiwar Compound, 6th Settlement, New Cairo</t>
   </si>
   <si>
@@ -172,6 +208,9 @@
     <t>AP008</t>
   </si>
   <si>
+    <t>Taj City, 5th Settlement</t>
+  </si>
+  <si>
     <t>Taj City, 5th Settlement, New Cairo</t>
   </si>
   <si>
@@ -184,6 +223,9 @@
     <t>AP009</t>
   </si>
   <si>
+    <t>Beta Greens, Mostakbal City</t>
+  </si>
+  <si>
     <t>Beta Greens, Mostakbal City, New Cairo</t>
   </si>
   <si>
@@ -199,6 +241,9 @@
     <t>AP010</t>
   </si>
   <si>
+    <t>Cavali Residence, 5th Settlement</t>
+  </si>
+  <si>
     <t>Cavali Residence, 5th Settlement, New Cairo</t>
   </si>
   <si>
@@ -214,6 +259,12 @@
     <t>AP011</t>
   </si>
   <si>
+    <t xml:space="preserve"> New Administrative Capital</t>
+  </si>
+  <si>
+    <t>Lumia Lagoons, R8 District</t>
+  </si>
+  <si>
     <t>Lumia Lagoons, R8 District, New Administrative Capital</t>
   </si>
   <si>
@@ -229,6 +280,9 @@
     <t>AP012</t>
   </si>
   <si>
+    <t>Armonia</t>
+  </si>
+  <si>
     <t>Armonia, New Administrative Capital</t>
   </si>
   <si>
@@ -244,6 +298,9 @@
     <t>AP013</t>
   </si>
   <si>
+    <t>Lake View Residence, 5th Settlement</t>
+  </si>
+  <si>
     <t>Lake View Residence, 5th Settlement, New Cairo</t>
   </si>
   <si>
@@ -259,6 +316,9 @@
     <t>AP014</t>
   </si>
   <si>
+    <t>Taj City, Lake Park Phase, 5th Settlement</t>
+  </si>
+  <si>
     <t>Taj City, Lake Park Phase, 5th Settlement, New Cairo</t>
   </si>
   <si>
@@ -274,6 +334,9 @@
     <t>AP015</t>
   </si>
   <si>
+    <t>Park Residence, Taj City, 5th Settlement</t>
+  </si>
+  <si>
     <t>Park Residence, Taj City, 5th Settlement, New Cairo</t>
   </si>
   <si>
@@ -289,6 +352,9 @@
     <t>townhouse</t>
   </si>
   <si>
+    <t>Mountain View iCity, 5th Settlement</t>
+  </si>
+  <si>
     <t>Mountain View iCity, 5th Settlement, New Cairo</t>
   </si>
   <si>
@@ -304,6 +370,9 @@
     <t>TH002</t>
   </si>
   <si>
+    <t>Green Square, Mostakbal City</t>
+  </si>
+  <si>
     <t>Green Square, Mostakbal City, New Cairo</t>
   </si>
   <si>
@@ -316,6 +385,9 @@
     <t>TH003</t>
   </si>
   <si>
+    <t>Saada Compound</t>
+  </si>
+  <si>
     <t>Saada Compound, New Cairo</t>
   </si>
   <si>
@@ -328,6 +400,9 @@
     <t>TH004</t>
   </si>
   <si>
+    <t>Palm Hills Katameya Extension, 5th Settlement</t>
+  </si>
+  <si>
     <t>Palm Hills Katameya Extension, 5th Settlement, New Cairo</t>
   </si>
   <si>
@@ -337,6 +412,9 @@
     <t>TH005</t>
   </si>
   <si>
+    <t>Eastshire Compound, 5th Settlement</t>
+  </si>
+  <si>
     <t>Eastshire Compound, 5th Settlement, New Cairo</t>
   </si>
   <si>
@@ -349,6 +427,9 @@
     <t>TH006</t>
   </si>
   <si>
+    <t>City Gate, 5th Settlement</t>
+  </si>
+  <si>
     <t>City Gate, 5th Settlement, New Cairo</t>
   </si>
   <si>
@@ -364,6 +445,9 @@
     <t>TH007</t>
   </si>
   <si>
+    <t>Modon Golf Town, 6th Settlement</t>
+  </si>
+  <si>
     <t>Modon Golf Town, 6th Settlement, New Cairo</t>
   </si>
   <si>
@@ -379,6 +463,9 @@
     <t>TH008</t>
   </si>
   <si>
+    <t>Al Maqsad Compound</t>
+  </si>
+  <si>
     <t>Al Maqsad Compound, New Administrative Capital</t>
   </si>
   <si>
@@ -391,6 +478,9 @@
     <t>TH009</t>
   </si>
   <si>
+    <t>Azzar 2 Compound, 5th Settlement</t>
+  </si>
+  <si>
     <t>Azzar 2 Compound, 5th Settlement, New Cairo</t>
   </si>
   <si>
@@ -403,6 +493,9 @@
     <t>TH010</t>
   </si>
   <si>
+    <t>Garden Residence, Hyde Park, 5th Settlement</t>
+  </si>
+  <si>
     <t>Garden Residence, Hyde Park, 5th Settlement, New Cairo</t>
   </si>
   <si>
@@ -418,6 +511,9 @@
     <t>TH011</t>
   </si>
   <si>
+    <t>Mivida, 5th Settlement</t>
+  </si>
+  <si>
     <t>Mivida, 5th Settlement, New Cairo</t>
   </si>
   <si>
@@ -430,6 +526,9 @@
     <t>TH012</t>
   </si>
   <si>
+    <t>Palm Hills New Cairo, 5th Settlement</t>
+  </si>
+  <si>
     <t>Palm Hills New Cairo, 5th Settlement, New Cairo</t>
   </si>
   <si>
@@ -451,6 +550,9 @@
     <t>penthouse</t>
   </si>
   <si>
+    <t>Promenade New Cairo, 5th Settlement</t>
+  </si>
+  <si>
     <t>Promenade New Cairo, 5th Settlement, New Cairo</t>
   </si>
   <si>
@@ -466,6 +568,9 @@
     <t>PH002</t>
   </si>
   <si>
+    <t>Stone Residence, 5th Settlement</t>
+  </si>
+  <si>
     <t>Stone Residence, 5th Settlement, New Cairo</t>
   </si>
   <si>
@@ -478,6 +583,9 @@
     <t>PH003</t>
   </si>
   <si>
+    <t>Moon Residences, Fifth Square, 5th Settlement</t>
+  </si>
+  <si>
     <t>Moon Residences, Fifth Square, 5th Settlement, New Cairo</t>
   </si>
   <si>
@@ -505,6 +613,9 @@
     <t>PH006</t>
   </si>
   <si>
+    <t>Mountain View Hyde Park, 5th Settlement</t>
+  </si>
+  <si>
     <t>Mountain View Hyde Park, 5th Settlement, New Cairo</t>
   </si>
   <si>
@@ -523,6 +634,9 @@
     <t>duplex</t>
   </si>
   <si>
+    <t>El Banafseg 12 Villas</t>
+  </si>
+  <si>
     <t>El Banafseg 12 Villas, New Cairo</t>
   </si>
   <si>
@@ -535,6 +649,9 @@
     <t>DU002</t>
   </si>
   <si>
+    <t>Mountain View iCity, Lagoon Park Phase, 5th Settlement</t>
+  </si>
+  <si>
     <t>Mountain View iCity, Lagoon Park Phase, 5th Settlement, New Cairo</t>
   </si>
   <si>
@@ -547,6 +664,9 @@
     <t>DU003</t>
   </si>
   <si>
+    <t>Mountain View iCity, MV Park Phase, 5th Settlement</t>
+  </si>
+  <si>
     <t>Mountain View iCity, MV Park Phase, 5th Settlement, New Cairo</t>
   </si>
   <si>
@@ -554,6 +674,9 @@
   </si>
   <si>
     <t>DU004</t>
+  </si>
+  <si>
+    <t>DeJoya 4, R8 District</t>
   </si>
   <si>
     <t>DeJoya 4, R8 District, New Administrative Capital</t>
@@ -1434,16 +1557,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26C9B937-F8EF-4B54-92F9-4D5F8A7910C9}">
-  <dimension ref="A1:K40"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EE2BFA6-D7EC-447B-BB51-A4EC2B87DAD0}">
+  <dimension ref="A1:M40"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="3" max="3" width="55.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="27.77734375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="145.5546875" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1477,1370 +1595,1610 @@
       <c r="K1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2">
+        <v>15</v>
+      </c>
+      <c r="D2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2">
         <v>3</v>
       </c>
-      <c r="E2">
+      <c r="G2">
         <v>3</v>
       </c>
-      <c r="F2">
+      <c r="H2">
         <v>160</v>
       </c>
-      <c r="G2" t="s">
+      <c r="I2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2">
+        <v>13000000</v>
+      </c>
+      <c r="K2" t="s">
+        <v>19</v>
+      </c>
+      <c r="L2" t="s">
+        <v>20</v>
+      </c>
+      <c r="M2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>70</v>
+      </c>
+      <c r="I3" t="s">
+        <v>26</v>
+      </c>
+      <c r="J3">
+        <v>6000000</v>
+      </c>
+      <c r="K3" t="s">
+        <v>27</v>
+      </c>
+      <c r="L3" t="s">
+        <v>28</v>
+      </c>
+      <c r="M3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B4" t="s">
         <v>14</v>
       </c>
-      <c r="H2">
-        <v>13000000</v>
-      </c>
-      <c r="I2" t="s">
+      <c r="C4" t="s">
         <v>15</v>
       </c>
-      <c r="J2" t="s">
-        <v>16</v>
-      </c>
-      <c r="K2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="D4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F4">
+        <v>3</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+      <c r="H4">
+        <v>144</v>
+      </c>
+      <c r="I4" t="s">
+        <v>32</v>
+      </c>
+      <c r="J4">
+        <v>3500000</v>
+      </c>
+      <c r="K4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L4" t="s">
+        <v>34</v>
+      </c>
+      <c r="M4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D5" t="s">
+        <v>37</v>
+      </c>
+      <c r="E5" t="s">
+        <v>38</v>
+      </c>
+      <c r="F5">
+        <v>3</v>
+      </c>
+      <c r="G5">
+        <v>4</v>
+      </c>
+      <c r="H5">
+        <v>176</v>
+      </c>
+      <c r="I5" t="s">
+        <v>39</v>
+      </c>
+      <c r="J5">
+        <v>22936160</v>
+      </c>
+      <c r="K5" t="s">
+        <v>40</v>
+      </c>
+      <c r="L5" t="s">
+        <v>41</v>
+      </c>
+      <c r="M5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" t="s">
+        <v>43</v>
+      </c>
+      <c r="D6" t="s">
+        <v>44</v>
+      </c>
+      <c r="E6" t="s">
+        <v>45</v>
+      </c>
+      <c r="F6">
+        <v>3</v>
+      </c>
+      <c r="G6">
+        <v>3</v>
+      </c>
+      <c r="H6">
+        <v>147</v>
+      </c>
+      <c r="I6" t="s">
+        <v>46</v>
+      </c>
+      <c r="J6">
+        <v>7500000</v>
+      </c>
+      <c r="K6" t="s">
+        <v>47</v>
+      </c>
+      <c r="L6" t="s">
+        <v>48</v>
+      </c>
+      <c r="M6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>49</v>
+      </c>
+      <c r="B7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" t="s">
+        <v>50</v>
+      </c>
+      <c r="E7" t="s">
+        <v>51</v>
+      </c>
+      <c r="F7">
+        <v>3</v>
+      </c>
+      <c r="G7">
+        <v>2</v>
+      </c>
+      <c r="H7">
+        <v>186</v>
+      </c>
+      <c r="I7" t="s">
+        <v>52</v>
+      </c>
+      <c r="J7">
+        <v>7500000</v>
+      </c>
+      <c r="K7" t="s">
+        <v>53</v>
+      </c>
+      <c r="L7" t="s">
+        <v>54</v>
+      </c>
+      <c r="M7" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>55</v>
+      </c>
+      <c r="B8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8" t="s">
+        <v>56</v>
+      </c>
+      <c r="E8" t="s">
+        <v>57</v>
+      </c>
+      <c r="F8">
+        <v>2</v>
+      </c>
+      <c r="G8">
+        <v>2</v>
+      </c>
+      <c r="H8">
+        <v>101</v>
+      </c>
+      <c r="I8" t="s">
+        <v>58</v>
+      </c>
+      <c r="J8">
+        <v>4000000</v>
+      </c>
+      <c r="K8" t="s">
+        <v>59</v>
+      </c>
+      <c r="L8" t="s">
+        <v>60</v>
+      </c>
+      <c r="M8" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>61</v>
+      </c>
+      <c r="B9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" t="s">
+        <v>62</v>
+      </c>
+      <c r="E9" t="s">
+        <v>63</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="G9">
+        <v>2</v>
+      </c>
+      <c r="H9">
+        <v>100</v>
+      </c>
+      <c r="I9" t="s">
+        <v>52</v>
+      </c>
+      <c r="J9">
+        <v>5500000</v>
+      </c>
+      <c r="K9" t="s">
+        <v>64</v>
+      </c>
+      <c r="L9" t="s">
+        <v>65</v>
+      </c>
+      <c r="M9" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>66</v>
+      </c>
+      <c r="B10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" t="s">
+        <v>67</v>
+      </c>
+      <c r="E10" t="s">
+        <v>68</v>
+      </c>
+      <c r="F10">
+        <v>2</v>
+      </c>
+      <c r="G10">
+        <v>2</v>
+      </c>
+      <c r="H10">
+        <v>127</v>
+      </c>
+      <c r="I10" t="s">
+        <v>69</v>
+      </c>
+      <c r="J10">
+        <v>3000000</v>
+      </c>
+      <c r="K10" t="s">
+        <v>70</v>
+      </c>
+      <c r="L10" t="s">
+        <v>71</v>
+      </c>
+      <c r="M10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>72</v>
+      </c>
+      <c r="B11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11" t="s">
+        <v>73</v>
+      </c>
+      <c r="E11" t="s">
+        <v>74</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+      <c r="H11">
+        <v>40</v>
+      </c>
+      <c r="I11" t="s">
+        <v>75</v>
+      </c>
+      <c r="J11">
+        <v>2000000</v>
+      </c>
+      <c r="K11" t="s">
+        <v>76</v>
+      </c>
+      <c r="L11" t="s">
+        <v>77</v>
+      </c>
+      <c r="M11" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>78</v>
+      </c>
+      <c r="B12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C12" t="s">
+        <v>79</v>
+      </c>
+      <c r="D12" t="s">
+        <v>80</v>
+      </c>
+      <c r="E12" t="s">
+        <v>81</v>
+      </c>
+      <c r="F12">
+        <v>3</v>
+      </c>
+      <c r="G12">
+        <v>2</v>
+      </c>
+      <c r="H12">
+        <v>136</v>
+      </c>
+      <c r="I12" t="s">
+        <v>82</v>
+      </c>
+      <c r="J12">
+        <v>6100000</v>
+      </c>
+      <c r="K12" t="s">
+        <v>83</v>
+      </c>
+      <c r="L12" t="s">
+        <v>84</v>
+      </c>
+      <c r="M12" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>85</v>
+      </c>
+      <c r="B13" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" t="s">
+        <v>79</v>
+      </c>
+      <c r="D13" t="s">
+        <v>86</v>
+      </c>
+      <c r="E13" t="s">
+        <v>87</v>
+      </c>
+      <c r="F13">
+        <v>3</v>
+      </c>
+      <c r="G13">
+        <v>3</v>
+      </c>
+      <c r="H13">
+        <v>154</v>
+      </c>
+      <c r="I13" t="s">
+        <v>88</v>
+      </c>
+      <c r="J13">
+        <v>5200000</v>
+      </c>
+      <c r="K13" t="s">
+        <v>89</v>
+      </c>
+      <c r="L13" t="s">
+        <v>90</v>
+      </c>
+      <c r="M13" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>91</v>
+      </c>
+      <c r="B14" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14" t="s">
+        <v>15</v>
+      </c>
+      <c r="D14" t="s">
+        <v>92</v>
+      </c>
+      <c r="E14" t="s">
+        <v>93</v>
+      </c>
+      <c r="F14">
+        <v>2</v>
+      </c>
+      <c r="G14">
+        <v>2</v>
+      </c>
+      <c r="H14">
+        <v>136</v>
+      </c>
+      <c r="I14" t="s">
+        <v>94</v>
+      </c>
+      <c r="J14">
+        <v>10700000</v>
+      </c>
+      <c r="K14" t="s">
+        <v>95</v>
+      </c>
+      <c r="L14" t="s">
+        <v>96</v>
+      </c>
+      <c r="M14" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>97</v>
+      </c>
+      <c r="B15" t="s">
+        <v>23</v>
+      </c>
+      <c r="C15" t="s">
+        <v>15</v>
+      </c>
+      <c r="D15" t="s">
+        <v>98</v>
+      </c>
+      <c r="E15" t="s">
+        <v>99</v>
+      </c>
+      <c r="F15">
+        <v>1</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
+      <c r="H15">
+        <v>63</v>
+      </c>
+      <c r="I15" t="s">
+        <v>100</v>
+      </c>
+      <c r="J15">
+        <v>3958900</v>
+      </c>
+      <c r="K15" t="s">
+        <v>101</v>
+      </c>
+      <c r="L15" t="s">
+        <v>102</v>
+      </c>
+      <c r="M15" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>103</v>
+      </c>
+      <c r="B16" t="s">
+        <v>14</v>
+      </c>
+      <c r="C16" t="s">
+        <v>15</v>
+      </c>
+      <c r="D16" t="s">
+        <v>104</v>
+      </c>
+      <c r="E16" t="s">
+        <v>105</v>
+      </c>
+      <c r="F16">
+        <v>3</v>
+      </c>
+      <c r="G16">
+        <v>3</v>
+      </c>
+      <c r="H16">
+        <v>170</v>
+      </c>
+      <c r="I16" t="s">
+        <v>52</v>
+      </c>
+      <c r="J16">
+        <v>8400000</v>
+      </c>
+      <c r="K16" t="s">
+        <v>106</v>
+      </c>
+      <c r="L16" t="s">
+        <v>107</v>
+      </c>
+      <c r="M16" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>108</v>
+      </c>
+      <c r="B17" t="s">
+        <v>109</v>
+      </c>
+      <c r="C17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D17" t="s">
+        <v>110</v>
+      </c>
+      <c r="E17" t="s">
+        <v>111</v>
+      </c>
+      <c r="F17">
+        <v>3</v>
+      </c>
+      <c r="G17">
+        <v>4</v>
+      </c>
+      <c r="H17">
+        <v>205</v>
+      </c>
+      <c r="I17" t="s">
+        <v>112</v>
+      </c>
+      <c r="J17">
+        <v>12500000</v>
+      </c>
+      <c r="K17" t="s">
+        <v>113</v>
+      </c>
+      <c r="L17" t="s">
+        <v>114</v>
+      </c>
+      <c r="M17" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>115</v>
+      </c>
+      <c r="B18" t="s">
+        <v>109</v>
+      </c>
+      <c r="C18" t="s">
+        <v>15</v>
+      </c>
+      <c r="D18" t="s">
+        <v>116</v>
+      </c>
+      <c r="E18" t="s">
+        <v>117</v>
+      </c>
+      <c r="F18">
+        <v>3</v>
+      </c>
+      <c r="G18">
+        <v>3</v>
+      </c>
+      <c r="H18">
+        <v>240</v>
+      </c>
+      <c r="I18" t="s">
         <v>18</v>
       </c>
-      <c r="B3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D3">
+      <c r="J18">
+        <v>9500000</v>
+      </c>
+      <c r="K18" t="s">
+        <v>118</v>
+      </c>
+      <c r="L18" t="s">
+        <v>119</v>
+      </c>
+      <c r="M18" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>120</v>
+      </c>
+      <c r="B19" t="s">
+        <v>109</v>
+      </c>
+      <c r="C19" t="s">
+        <v>15</v>
+      </c>
+      <c r="D19" t="s">
+        <v>121</v>
+      </c>
+      <c r="E19" t="s">
+        <v>122</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>199</v>
+      </c>
+      <c r="I19" t="s">
+        <v>52</v>
+      </c>
+      <c r="J19">
+        <v>18337300</v>
+      </c>
+      <c r="K19" t="s">
+        <v>123</v>
+      </c>
+      <c r="L19" t="s">
+        <v>124</v>
+      </c>
+      <c r="M19" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>125</v>
+      </c>
+      <c r="B20" t="s">
+        <v>109</v>
+      </c>
+      <c r="C20" t="s">
+        <v>15</v>
+      </c>
+      <c r="D20" t="s">
+        <v>126</v>
+      </c>
+      <c r="E20" t="s">
+        <v>127</v>
+      </c>
+      <c r="F20">
+        <v>5</v>
+      </c>
+      <c r="G20">
+        <v>5</v>
+      </c>
+      <c r="H20">
+        <v>280</v>
+      </c>
+      <c r="I20" t="s">
+        <v>52</v>
+      </c>
+      <c r="J20">
+        <v>21500000</v>
+      </c>
+      <c r="K20" t="s">
+        <v>123</v>
+      </c>
+      <c r="L20" t="s">
+        <v>128</v>
+      </c>
+      <c r="M20" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>129</v>
+      </c>
+      <c r="B21" t="s">
+        <v>109</v>
+      </c>
+      <c r="C21" t="s">
+        <v>15</v>
+      </c>
+      <c r="D21" t="s">
+        <v>130</v>
+      </c>
+      <c r="E21" t="s">
+        <v>131</v>
+      </c>
+      <c r="F21">
+        <v>3</v>
+      </c>
+      <c r="G21">
+        <v>4</v>
+      </c>
+      <c r="H21">
+        <v>166</v>
+      </c>
+      <c r="I21" t="s">
+        <v>52</v>
+      </c>
+      <c r="J21">
+        <v>10499900</v>
+      </c>
+      <c r="K21" t="s">
+        <v>132</v>
+      </c>
+      <c r="L21" t="s">
+        <v>133</v>
+      </c>
+      <c r="M21" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>134</v>
+      </c>
+      <c r="B22" t="s">
+        <v>109</v>
+      </c>
+      <c r="C22" t="s">
+        <v>15</v>
+      </c>
+      <c r="D22" t="s">
+        <v>135</v>
+      </c>
+      <c r="E22" t="s">
+        <v>136</v>
+      </c>
+      <c r="F22">
+        <v>3</v>
+      </c>
+      <c r="G22">
+        <v>4</v>
+      </c>
+      <c r="H22">
+        <v>253</v>
+      </c>
+      <c r="I22" t="s">
+        <v>137</v>
+      </c>
+      <c r="J22">
+        <v>16400000</v>
+      </c>
+      <c r="K22" t="s">
+        <v>138</v>
+      </c>
+      <c r="L22" t="s">
+        <v>139</v>
+      </c>
+      <c r="M22" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>140</v>
+      </c>
+      <c r="B23" t="s">
+        <v>109</v>
+      </c>
+      <c r="C23" t="s">
+        <v>15</v>
+      </c>
+      <c r="D23" t="s">
+        <v>141</v>
+      </c>
+      <c r="E23" t="s">
+        <v>142</v>
+      </c>
+      <c r="F23">
+        <v>5</v>
+      </c>
+      <c r="G23">
+        <v>4</v>
+      </c>
+      <c r="H23">
+        <v>180</v>
+      </c>
+      <c r="I23" t="s">
+        <v>143</v>
+      </c>
+      <c r="J23">
+        <v>10200000</v>
+      </c>
+      <c r="K23" t="s">
+        <v>144</v>
+      </c>
+      <c r="L23" t="s">
+        <v>145</v>
+      </c>
+      <c r="M23" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>146</v>
+      </c>
+      <c r="B24" t="s">
+        <v>109</v>
+      </c>
+      <c r="C24" t="s">
+        <v>79</v>
+      </c>
+      <c r="D24" t="s">
+        <v>147</v>
+      </c>
+      <c r="E24" t="s">
+        <v>148</v>
+      </c>
+      <c r="F24">
+        <v>4</v>
+      </c>
+      <c r="G24">
+        <v>4</v>
+      </c>
+      <c r="H24">
+        <v>392</v>
+      </c>
+      <c r="I24" t="s">
+        <v>149</v>
+      </c>
+      <c r="J24">
+        <v>15717417</v>
+      </c>
+      <c r="K24" t="s">
+        <v>123</v>
+      </c>
+      <c r="L24" t="s">
+        <v>150</v>
+      </c>
+      <c r="M24" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>151</v>
+      </c>
+      <c r="B25" t="s">
+        <v>109</v>
+      </c>
+      <c r="C25" t="s">
+        <v>15</v>
+      </c>
+      <c r="D25" t="s">
+        <v>152</v>
+      </c>
+      <c r="E25" t="s">
+        <v>153</v>
+      </c>
+      <c r="F25">
+        <v>5</v>
+      </c>
+      <c r="G25">
+        <v>5</v>
+      </c>
+      <c r="H25">
+        <v>225</v>
+      </c>
+      <c r="I25" t="s">
+        <v>52</v>
+      </c>
+      <c r="J25">
+        <v>15000000</v>
+      </c>
+      <c r="K25" t="s">
+        <v>154</v>
+      </c>
+      <c r="L25" t="s">
+        <v>155</v>
+      </c>
+      <c r="M25" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>156</v>
+      </c>
+      <c r="B26" t="s">
+        <v>109</v>
+      </c>
+      <c r="C26" t="s">
+        <v>15</v>
+      </c>
+      <c r="D26" t="s">
+        <v>157</v>
+      </c>
+      <c r="E26" t="s">
+        <v>158</v>
+      </c>
+      <c r="F26">
+        <v>3</v>
+      </c>
+      <c r="G26">
+        <v>3</v>
+      </c>
+      <c r="H26">
+        <v>209</v>
+      </c>
+      <c r="I26" t="s">
+        <v>159</v>
+      </c>
+      <c r="J26">
+        <v>14800000</v>
+      </c>
+      <c r="K26" t="s">
+        <v>160</v>
+      </c>
+      <c r="L26" t="s">
+        <v>161</v>
+      </c>
+      <c r="M26" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>162</v>
+      </c>
+      <c r="B27" t="s">
+        <v>109</v>
+      </c>
+      <c r="C27" t="s">
+        <v>15</v>
+      </c>
+      <c r="D27" t="s">
+        <v>163</v>
+      </c>
+      <c r="E27" t="s">
+        <v>164</v>
+      </c>
+      <c r="F27">
+        <v>3</v>
+      </c>
+      <c r="G27">
+        <v>4</v>
+      </c>
+      <c r="H27">
+        <v>190</v>
+      </c>
+      <c r="I27" t="s">
+        <v>18</v>
+      </c>
+      <c r="J27">
+        <v>27000000</v>
+      </c>
+      <c r="K27" t="s">
+        <v>165</v>
+      </c>
+      <c r="L27" t="s">
+        <v>166</v>
+      </c>
+      <c r="M27" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>167</v>
+      </c>
+      <c r="B28" t="s">
+        <v>109</v>
+      </c>
+      <c r="C28" t="s">
+        <v>15</v>
+      </c>
+      <c r="D28" t="s">
+        <v>168</v>
+      </c>
+      <c r="E28" t="s">
+        <v>169</v>
+      </c>
+      <c r="F28">
+        <v>4</v>
+      </c>
+      <c r="G28">
+        <v>4</v>
+      </c>
+      <c r="H28">
+        <v>260</v>
+      </c>
+      <c r="I28" t="s">
+        <v>82</v>
+      </c>
+      <c r="J28">
+        <v>14500000</v>
+      </c>
+      <c r="K28" t="s">
+        <v>170</v>
+      </c>
+      <c r="L28" t="s">
+        <v>171</v>
+      </c>
+      <c r="M28" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>172</v>
+      </c>
+      <c r="B29" t="s">
+        <v>109</v>
+      </c>
+      <c r="C29" t="s">
+        <v>15</v>
+      </c>
+      <c r="D29" t="s">
+        <v>157</v>
+      </c>
+      <c r="E29" t="s">
+        <v>158</v>
+      </c>
+      <c r="F29">
+        <v>4</v>
+      </c>
+      <c r="G29">
+        <v>4</v>
+      </c>
+      <c r="H29">
+        <v>250</v>
+      </c>
+      <c r="I29" t="s">
+        <v>18</v>
+      </c>
+      <c r="J29">
+        <v>12300000</v>
+      </c>
+      <c r="K29" t="s">
+        <v>160</v>
+      </c>
+      <c r="L29" t="s">
+        <v>173</v>
+      </c>
+      <c r="M29" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>174</v>
+      </c>
+      <c r="B30" t="s">
+        <v>175</v>
+      </c>
+      <c r="C30" t="s">
+        <v>15</v>
+      </c>
+      <c r="D30" t="s">
+        <v>176</v>
+      </c>
+      <c r="E30" t="s">
+        <v>177</v>
+      </c>
+      <c r="F30">
+        <v>4</v>
+      </c>
+      <c r="G30">
+        <v>4</v>
+      </c>
+      <c r="H30">
+        <v>245</v>
+      </c>
+      <c r="I30" t="s">
+        <v>178</v>
+      </c>
+      <c r="J30">
+        <v>6500000</v>
+      </c>
+      <c r="K30" t="s">
+        <v>179</v>
+      </c>
+      <c r="L30" t="s">
+        <v>180</v>
+      </c>
+      <c r="M30" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>181</v>
+      </c>
+      <c r="B31" t="s">
+        <v>175</v>
+      </c>
+      <c r="C31" t="s">
+        <v>15</v>
+      </c>
+      <c r="D31" t="s">
+        <v>182</v>
+      </c>
+      <c r="E31" t="s">
+        <v>183</v>
+      </c>
+      <c r="F31">
+        <v>4</v>
+      </c>
+      <c r="G31">
         <v>1</v>
       </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>70</v>
-      </c>
-      <c r="G3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H3">
-        <v>6000000</v>
-      </c>
-      <c r="I3" t="s">
-        <v>22</v>
-      </c>
-      <c r="J3" t="s">
-        <v>23</v>
-      </c>
-      <c r="K3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D4">
+      <c r="H31">
+        <v>220</v>
+      </c>
+      <c r="I31" t="s">
+        <v>52</v>
+      </c>
+      <c r="J31">
+        <v>4000000</v>
+      </c>
+      <c r="K31" t="s">
+        <v>184</v>
+      </c>
+      <c r="L31" t="s">
+        <v>185</v>
+      </c>
+      <c r="M31" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>186</v>
+      </c>
+      <c r="B32" t="s">
+        <v>175</v>
+      </c>
+      <c r="C32" t="s">
+        <v>15</v>
+      </c>
+      <c r="D32" t="s">
+        <v>187</v>
+      </c>
+      <c r="E32" t="s">
+        <v>188</v>
+      </c>
+      <c r="F32">
         <v>3</v>
       </c>
-      <c r="E4">
+      <c r="G32">
+        <v>3</v>
+      </c>
+      <c r="H32">
+        <v>175</v>
+      </c>
+      <c r="I32" t="s">
+        <v>52</v>
+      </c>
+      <c r="J32">
+        <v>10000000</v>
+      </c>
+      <c r="K32" t="s">
+        <v>160</v>
+      </c>
+      <c r="L32" t="s">
+        <v>189</v>
+      </c>
+      <c r="M32" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>190</v>
+      </c>
+      <c r="B33" t="s">
+        <v>175</v>
+      </c>
+      <c r="C33" t="s">
+        <v>15</v>
+      </c>
+      <c r="D33" t="s">
+        <v>110</v>
+      </c>
+      <c r="E33" t="s">
+        <v>111</v>
+      </c>
+      <c r="F33">
+        <v>4</v>
+      </c>
+      <c r="G33">
         <v>2</v>
       </c>
-      <c r="F4">
-        <v>144</v>
-      </c>
-      <c r="G4" t="s">
-        <v>26</v>
-      </c>
-      <c r="H4">
-        <v>3500000</v>
-      </c>
-      <c r="I4" t="s">
-        <v>27</v>
-      </c>
-      <c r="J4" t="s">
-        <v>28</v>
-      </c>
-      <c r="K4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>29</v>
-      </c>
-      <c r="B5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D5">
+      <c r="H33">
+        <v>205</v>
+      </c>
+      <c r="I33" t="s">
+        <v>52</v>
+      </c>
+      <c r="J33">
+        <v>8000000</v>
+      </c>
+      <c r="K33" t="s">
+        <v>191</v>
+      </c>
+      <c r="L33" t="s">
+        <v>192</v>
+      </c>
+      <c r="M33" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>193</v>
+      </c>
+      <c r="B34" t="s">
+        <v>175</v>
+      </c>
+      <c r="C34" t="s">
+        <v>15</v>
+      </c>
+      <c r="D34" t="s">
+        <v>182</v>
+      </c>
+      <c r="E34" t="s">
+        <v>183</v>
+      </c>
+      <c r="F34">
         <v>3</v>
       </c>
-      <c r="E5">
+      <c r="G34">
+        <v>3</v>
+      </c>
+      <c r="H34">
+        <v>220</v>
+      </c>
+      <c r="I34" t="s">
+        <v>52</v>
+      </c>
+      <c r="J34">
+        <v>8000000</v>
+      </c>
+      <c r="K34" t="s">
+        <v>194</v>
+      </c>
+      <c r="L34" t="s">
+        <v>195</v>
+      </c>
+      <c r="M34" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>196</v>
+      </c>
+      <c r="B35" t="s">
+        <v>175</v>
+      </c>
+      <c r="C35" t="s">
+        <v>15</v>
+      </c>
+      <c r="D35" t="s">
+        <v>197</v>
+      </c>
+      <c r="E35" t="s">
+        <v>198</v>
+      </c>
+      <c r="F35">
+        <v>3</v>
+      </c>
+      <c r="G35">
+        <v>2</v>
+      </c>
+      <c r="H35">
+        <v>166</v>
+      </c>
+      <c r="I35" t="s">
+        <v>199</v>
+      </c>
+      <c r="J35">
+        <v>10500000</v>
+      </c>
+      <c r="K35" t="s">
+        <v>200</v>
+      </c>
+      <c r="L35" t="s">
+        <v>201</v>
+      </c>
+      <c r="M35" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>202</v>
+      </c>
+      <c r="B36" t="s">
+        <v>203</v>
+      </c>
+      <c r="C36" t="s">
+        <v>15</v>
+      </c>
+      <c r="D36" t="s">
+        <v>204</v>
+      </c>
+      <c r="E36" t="s">
+        <v>205</v>
+      </c>
+      <c r="F36">
+        <v>5</v>
+      </c>
+      <c r="G36">
+        <v>3</v>
+      </c>
+      <c r="H36">
+        <v>300</v>
+      </c>
+      <c r="I36" t="s">
+        <v>18</v>
+      </c>
+      <c r="J36">
+        <v>8000000</v>
+      </c>
+      <c r="K36" t="s">
+        <v>206</v>
+      </c>
+      <c r="L36" t="s">
+        <v>207</v>
+      </c>
+      <c r="M36" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>208</v>
+      </c>
+      <c r="B37" t="s">
+        <v>203</v>
+      </c>
+      <c r="C37" t="s">
+        <v>15</v>
+      </c>
+      <c r="D37" t="s">
+        <v>209</v>
+      </c>
+      <c r="E37" t="s">
+        <v>210</v>
+      </c>
+      <c r="F37">
+        <v>3</v>
+      </c>
+      <c r="G37">
         <v>4</v>
       </c>
-      <c r="F5">
-        <v>176</v>
-      </c>
-      <c r="G5" t="s">
-        <v>31</v>
-      </c>
-      <c r="H5">
-        <v>22936160</v>
-      </c>
-      <c r="I5" t="s">
-        <v>32</v>
-      </c>
-      <c r="J5" t="s">
-        <v>33</v>
-      </c>
-      <c r="K5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>34</v>
-      </c>
-      <c r="B6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" t="s">
-        <v>35</v>
-      </c>
-      <c r="D6">
+      <c r="H37">
+        <v>235</v>
+      </c>
+      <c r="I37" t="s">
+        <v>82</v>
+      </c>
+      <c r="J37">
+        <v>9600000</v>
+      </c>
+      <c r="K37" t="s">
+        <v>211</v>
+      </c>
+      <c r="L37" t="s">
+        <v>212</v>
+      </c>
+      <c r="M37" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>213</v>
+      </c>
+      <c r="B38" t="s">
+        <v>203</v>
+      </c>
+      <c r="C38" t="s">
+        <v>15</v>
+      </c>
+      <c r="D38" t="s">
+        <v>214</v>
+      </c>
+      <c r="E38" t="s">
+        <v>215</v>
+      </c>
+      <c r="F38">
         <v>3</v>
       </c>
-      <c r="E6">
+      <c r="G38">
         <v>3</v>
       </c>
-      <c r="F6">
-        <v>147</v>
-      </c>
-      <c r="G6" t="s">
-        <v>36</v>
-      </c>
-      <c r="H6">
-        <v>7500000</v>
-      </c>
-      <c r="I6" t="s">
-        <v>37</v>
-      </c>
-      <c r="J6" t="s">
-        <v>38</v>
-      </c>
-      <c r="K6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" t="s">
-        <v>40</v>
-      </c>
-      <c r="D7">
+      <c r="H38">
+        <v>235</v>
+      </c>
+      <c r="I38" t="s">
+        <v>52</v>
+      </c>
+      <c r="J38">
+        <v>10700000</v>
+      </c>
+      <c r="K38" t="s">
+        <v>211</v>
+      </c>
+      <c r="L38" t="s">
+        <v>216</v>
+      </c>
+      <c r="M38" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>217</v>
+      </c>
+      <c r="B39" t="s">
+        <v>203</v>
+      </c>
+      <c r="C39" t="s">
+        <v>79</v>
+      </c>
+      <c r="D39" t="s">
+        <v>218</v>
+      </c>
+      <c r="E39" t="s">
+        <v>219</v>
+      </c>
+      <c r="F39">
         <v>3</v>
       </c>
-      <c r="E7">
-        <v>2</v>
-      </c>
-      <c r="F7">
-        <v>186</v>
-      </c>
-      <c r="G7" t="s">
-        <v>41</v>
-      </c>
-      <c r="H7">
-        <v>7500000</v>
-      </c>
-      <c r="I7" t="s">
-        <v>42</v>
-      </c>
-      <c r="J7" t="s">
-        <v>43</v>
-      </c>
-      <c r="K7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>44</v>
-      </c>
-      <c r="B8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" t="s">
-        <v>45</v>
-      </c>
-      <c r="D8">
-        <v>2</v>
-      </c>
-      <c r="E8">
-        <v>2</v>
-      </c>
-      <c r="F8">
-        <v>101</v>
-      </c>
-      <c r="G8" t="s">
-        <v>46</v>
-      </c>
-      <c r="H8">
-        <v>4000000</v>
-      </c>
-      <c r="I8" t="s">
-        <v>47</v>
-      </c>
-      <c r="J8" t="s">
-        <v>48</v>
-      </c>
-      <c r="K8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>49</v>
-      </c>
-      <c r="B9" t="s">
-        <v>19</v>
-      </c>
-      <c r="C9" t="s">
-        <v>50</v>
-      </c>
-      <c r="D9">
-        <v>1</v>
-      </c>
-      <c r="E9">
-        <v>2</v>
-      </c>
-      <c r="F9">
-        <v>100</v>
-      </c>
-      <c r="G9" t="s">
-        <v>41</v>
-      </c>
-      <c r="H9">
-        <v>5500000</v>
-      </c>
-      <c r="I9" t="s">
-        <v>51</v>
-      </c>
-      <c r="J9" t="s">
+      <c r="G39">
+        <v>5</v>
+      </c>
+      <c r="H39">
+        <v>282</v>
+      </c>
+      <c r="I39" t="s">
         <v>52</v>
       </c>
-      <c r="K9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>53</v>
-      </c>
-      <c r="B10" t="s">
-        <v>12</v>
-      </c>
-      <c r="C10" t="s">
-        <v>54</v>
-      </c>
-      <c r="D10">
-        <v>2</v>
-      </c>
-      <c r="E10">
-        <v>2</v>
-      </c>
-      <c r="F10">
-        <v>127</v>
-      </c>
-      <c r="G10" t="s">
-        <v>55</v>
-      </c>
-      <c r="H10">
-        <v>3000000</v>
-      </c>
-      <c r="I10" t="s">
-        <v>56</v>
-      </c>
-      <c r="J10" t="s">
-        <v>57</v>
-      </c>
-      <c r="K10" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>58</v>
-      </c>
-      <c r="B11" t="s">
-        <v>19</v>
-      </c>
-      <c r="C11" t="s">
-        <v>59</v>
-      </c>
-      <c r="D11">
-        <v>1</v>
-      </c>
-      <c r="E11">
-        <v>1</v>
-      </c>
-      <c r="F11">
-        <v>40</v>
-      </c>
-      <c r="G11" t="s">
-        <v>60</v>
-      </c>
-      <c r="H11">
-        <v>2000000</v>
-      </c>
-      <c r="I11" t="s">
-        <v>61</v>
-      </c>
-      <c r="J11" t="s">
-        <v>62</v>
-      </c>
-      <c r="K11" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>63</v>
-      </c>
-      <c r="B12" t="s">
-        <v>12</v>
-      </c>
-      <c r="C12" t="s">
-        <v>64</v>
-      </c>
-      <c r="D12">
+      <c r="J39">
+        <v>7163000</v>
+      </c>
+      <c r="K39" t="s">
+        <v>220</v>
+      </c>
+      <c r="L39" t="s">
+        <v>221</v>
+      </c>
+      <c r="M39" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>222</v>
+      </c>
+      <c r="B40" t="s">
+        <v>203</v>
+      </c>
+      <c r="C40" t="s">
+        <v>15</v>
+      </c>
+      <c r="D40" t="s">
+        <v>157</v>
+      </c>
+      <c r="E40" t="s">
+        <v>158</v>
+      </c>
+      <c r="F40">
         <v>3</v>
       </c>
-      <c r="E12">
-        <v>2</v>
-      </c>
-      <c r="F12">
-        <v>136</v>
-      </c>
-      <c r="G12" t="s">
-        <v>65</v>
-      </c>
-      <c r="H12">
-        <v>6100000</v>
-      </c>
-      <c r="I12" t="s">
-        <v>66</v>
-      </c>
-      <c r="J12" t="s">
-        <v>67</v>
-      </c>
-      <c r="K12" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>68</v>
-      </c>
-      <c r="B13" t="s">
-        <v>12</v>
-      </c>
-      <c r="C13" t="s">
-        <v>69</v>
-      </c>
-      <c r="D13">
+      <c r="G40">
         <v>3</v>
       </c>
-      <c r="E13">
-        <v>3</v>
-      </c>
-      <c r="F13">
-        <v>154</v>
-      </c>
-      <c r="G13" t="s">
-        <v>70</v>
-      </c>
-      <c r="H13">
-        <v>5200000</v>
-      </c>
-      <c r="I13" t="s">
-        <v>71</v>
-      </c>
-      <c r="J13" t="s">
-        <v>72</v>
-      </c>
-      <c r="K13" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>73</v>
-      </c>
-      <c r="B14" t="s">
-        <v>12</v>
-      </c>
-      <c r="C14" t="s">
-        <v>74</v>
-      </c>
-      <c r="D14">
-        <v>2</v>
-      </c>
-      <c r="E14">
-        <v>2</v>
-      </c>
-      <c r="F14">
-        <v>136</v>
-      </c>
-      <c r="G14" t="s">
-        <v>75</v>
-      </c>
-      <c r="H14">
-        <v>10700000</v>
-      </c>
-      <c r="I14" t="s">
-        <v>76</v>
-      </c>
-      <c r="J14" t="s">
-        <v>77</v>
-      </c>
-      <c r="K14" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>78</v>
-      </c>
-      <c r="B15" t="s">
-        <v>19</v>
-      </c>
-      <c r="C15" t="s">
-        <v>79</v>
-      </c>
-      <c r="D15">
-        <v>1</v>
-      </c>
-      <c r="E15">
-        <v>1</v>
-      </c>
-      <c r="F15">
-        <v>63</v>
-      </c>
-      <c r="G15" t="s">
-        <v>80</v>
-      </c>
-      <c r="H15">
-        <v>3958900</v>
-      </c>
-      <c r="I15" t="s">
-        <v>81</v>
-      </c>
-      <c r="J15" t="s">
-        <v>82</v>
-      </c>
-      <c r="K15" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>83</v>
-      </c>
-      <c r="B16" t="s">
-        <v>12</v>
-      </c>
-      <c r="C16" t="s">
-        <v>84</v>
-      </c>
-      <c r="D16">
-        <v>3</v>
-      </c>
-      <c r="E16">
-        <v>3</v>
-      </c>
-      <c r="F16">
-        <v>170</v>
-      </c>
-      <c r="G16" t="s">
-        <v>41</v>
-      </c>
-      <c r="H16">
-        <v>8400000</v>
-      </c>
-      <c r="I16" t="s">
-        <v>85</v>
-      </c>
-      <c r="J16" t="s">
-        <v>86</v>
-      </c>
-      <c r="K16" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>87</v>
-      </c>
-      <c r="B17" t="s">
-        <v>88</v>
-      </c>
-      <c r="C17" t="s">
-        <v>89</v>
-      </c>
-      <c r="D17">
-        <v>3</v>
-      </c>
-      <c r="E17">
-        <v>4</v>
-      </c>
-      <c r="F17">
-        <v>205</v>
-      </c>
-      <c r="G17" t="s">
-        <v>90</v>
-      </c>
-      <c r="H17">
-        <v>12500000</v>
-      </c>
-      <c r="I17" t="s">
-        <v>91</v>
-      </c>
-      <c r="J17" t="s">
-        <v>92</v>
-      </c>
-      <c r="K17" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>93</v>
-      </c>
-      <c r="B18" t="s">
-        <v>88</v>
-      </c>
-      <c r="C18" t="s">
-        <v>94</v>
-      </c>
-      <c r="D18">
-        <v>3</v>
-      </c>
-      <c r="E18">
-        <v>3</v>
-      </c>
-      <c r="F18">
-        <v>240</v>
-      </c>
-      <c r="G18" t="s">
-        <v>14</v>
-      </c>
-      <c r="H18">
-        <v>9500000</v>
-      </c>
-      <c r="I18" t="s">
-        <v>95</v>
-      </c>
-      <c r="J18" t="s">
-        <v>96</v>
-      </c>
-      <c r="K18" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>97</v>
-      </c>
-      <c r="B19" t="s">
-        <v>88</v>
-      </c>
-      <c r="C19" t="s">
-        <v>98</v>
-      </c>
-      <c r="D19">
-        <v>0</v>
-      </c>
-      <c r="E19">
-        <v>0</v>
-      </c>
-      <c r="F19">
-        <v>199</v>
-      </c>
-      <c r="G19" t="s">
-        <v>41</v>
-      </c>
-      <c r="H19">
-        <v>18337300</v>
-      </c>
-      <c r="I19" t="s">
-        <v>99</v>
-      </c>
-      <c r="J19" t="s">
-        <v>100</v>
-      </c>
-      <c r="K19" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>101</v>
-      </c>
-      <c r="B20" t="s">
-        <v>88</v>
-      </c>
-      <c r="C20" t="s">
-        <v>102</v>
-      </c>
-      <c r="D20">
-        <v>5</v>
-      </c>
-      <c r="E20">
-        <v>5</v>
-      </c>
-      <c r="F20">
-        <v>280</v>
-      </c>
-      <c r="G20" t="s">
-        <v>41</v>
-      </c>
-      <c r="H20">
-        <v>21500000</v>
-      </c>
-      <c r="I20" t="s">
-        <v>99</v>
-      </c>
-      <c r="J20" t="s">
-        <v>103</v>
-      </c>
-      <c r="K20" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>104</v>
-      </c>
-      <c r="B21" t="s">
-        <v>88</v>
-      </c>
-      <c r="C21" t="s">
-        <v>105</v>
-      </c>
-      <c r="D21">
-        <v>3</v>
-      </c>
-      <c r="E21">
-        <v>4</v>
-      </c>
-      <c r="F21">
-        <v>166</v>
-      </c>
-      <c r="G21" t="s">
-        <v>41</v>
-      </c>
-      <c r="H21">
-        <v>10499900</v>
-      </c>
-      <c r="I21" t="s">
-        <v>106</v>
-      </c>
-      <c r="J21" t="s">
-        <v>107</v>
-      </c>
-      <c r="K21" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>108</v>
-      </c>
-      <c r="B22" t="s">
-        <v>88</v>
-      </c>
-      <c r="C22" t="s">
-        <v>109</v>
-      </c>
-      <c r="D22">
-        <v>3</v>
-      </c>
-      <c r="E22">
-        <v>4</v>
-      </c>
-      <c r="F22">
-        <v>253</v>
-      </c>
-      <c r="G22" t="s">
-        <v>110</v>
-      </c>
-      <c r="H22">
-        <v>16400000</v>
-      </c>
-      <c r="I22" t="s">
-        <v>111</v>
-      </c>
-      <c r="J22" t="s">
-        <v>112</v>
-      </c>
-      <c r="K22" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>113</v>
-      </c>
-      <c r="B23" t="s">
-        <v>88</v>
-      </c>
-      <c r="C23" t="s">
-        <v>114</v>
-      </c>
-      <c r="D23">
-        <v>5</v>
-      </c>
-      <c r="E23">
-        <v>4</v>
-      </c>
-      <c r="F23">
-        <v>180</v>
-      </c>
-      <c r="G23" t="s">
-        <v>115</v>
-      </c>
-      <c r="H23">
-        <v>10200000</v>
-      </c>
-      <c r="I23" t="s">
-        <v>116</v>
-      </c>
-      <c r="J23" t="s">
-        <v>117</v>
-      </c>
-      <c r="K23" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>118</v>
-      </c>
-      <c r="B24" t="s">
-        <v>88</v>
-      </c>
-      <c r="C24" t="s">
-        <v>119</v>
-      </c>
-      <c r="D24">
-        <v>4</v>
-      </c>
-      <c r="E24">
-        <v>4</v>
-      </c>
-      <c r="F24">
-        <v>392</v>
-      </c>
-      <c r="G24" t="s">
-        <v>120</v>
-      </c>
-      <c r="H24">
-        <v>15717417</v>
-      </c>
-      <c r="I24" t="s">
-        <v>99</v>
-      </c>
-      <c r="J24" t="s">
-        <v>121</v>
-      </c>
-      <c r="K24" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>122</v>
-      </c>
-      <c r="B25" t="s">
-        <v>88</v>
-      </c>
-      <c r="C25" t="s">
-        <v>123</v>
-      </c>
-      <c r="D25">
-        <v>5</v>
-      </c>
-      <c r="E25">
-        <v>5</v>
-      </c>
-      <c r="F25">
+      <c r="H40">
+        <v>211</v>
+      </c>
+      <c r="I40" t="s">
+        <v>223</v>
+      </c>
+      <c r="J40">
+        <v>13100000</v>
+      </c>
+      <c r="K40" t="s">
+        <v>224</v>
+      </c>
+      <c r="L40" t="s">
         <v>225</v>
       </c>
-      <c r="G25" t="s">
-        <v>41</v>
-      </c>
-      <c r="H25">
-        <v>15000000</v>
-      </c>
-      <c r="I25" t="s">
-        <v>124</v>
-      </c>
-      <c r="J25" t="s">
-        <v>125</v>
-      </c>
-      <c r="K25" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>126</v>
-      </c>
-      <c r="B26" t="s">
-        <v>88</v>
-      </c>
-      <c r="C26" t="s">
-        <v>127</v>
-      </c>
-      <c r="D26">
-        <v>3</v>
-      </c>
-      <c r="E26">
-        <v>3</v>
-      </c>
-      <c r="F26">
-        <v>209</v>
-      </c>
-      <c r="G26" t="s">
-        <v>128</v>
-      </c>
-      <c r="H26">
-        <v>14800000</v>
-      </c>
-      <c r="I26" t="s">
-        <v>129</v>
-      </c>
-      <c r="J26" t="s">
-        <v>130</v>
-      </c>
-      <c r="K26" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
-        <v>131</v>
-      </c>
-      <c r="B27" t="s">
-        <v>88</v>
-      </c>
-      <c r="C27" t="s">
-        <v>132</v>
-      </c>
-      <c r="D27">
-        <v>3</v>
-      </c>
-      <c r="E27">
-        <v>4</v>
-      </c>
-      <c r="F27">
-        <v>190</v>
-      </c>
-      <c r="G27" t="s">
-        <v>14</v>
-      </c>
-      <c r="H27">
-        <v>27000000</v>
-      </c>
-      <c r="I27" t="s">
-        <v>133</v>
-      </c>
-      <c r="J27" t="s">
-        <v>134</v>
-      </c>
-      <c r="K27" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
-        <v>135</v>
-      </c>
-      <c r="B28" t="s">
-        <v>88</v>
-      </c>
-      <c r="C28" t="s">
-        <v>136</v>
-      </c>
-      <c r="D28">
-        <v>4</v>
-      </c>
-      <c r="E28">
-        <v>4</v>
-      </c>
-      <c r="F28">
-        <v>260</v>
-      </c>
-      <c r="G28" t="s">
-        <v>65</v>
-      </c>
-      <c r="H28">
-        <v>14500000</v>
-      </c>
-      <c r="I28" t="s">
-        <v>137</v>
-      </c>
-      <c r="J28" t="s">
-        <v>138</v>
-      </c>
-      <c r="K28" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
-        <v>139</v>
-      </c>
-      <c r="B29" t="s">
-        <v>88</v>
-      </c>
-      <c r="C29" t="s">
-        <v>127</v>
-      </c>
-      <c r="D29">
-        <v>4</v>
-      </c>
-      <c r="E29">
-        <v>4</v>
-      </c>
-      <c r="F29">
-        <v>250</v>
-      </c>
-      <c r="G29" t="s">
-        <v>14</v>
-      </c>
-      <c r="H29">
-        <v>12300000</v>
-      </c>
-      <c r="I29" t="s">
-        <v>129</v>
-      </c>
-      <c r="J29" t="s">
-        <v>140</v>
-      </c>
-      <c r="K29" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
-        <v>141</v>
-      </c>
-      <c r="B30" t="s">
-        <v>142</v>
-      </c>
-      <c r="C30" t="s">
-        <v>143</v>
-      </c>
-      <c r="D30">
-        <v>4</v>
-      </c>
-      <c r="E30">
-        <v>4</v>
-      </c>
-      <c r="F30">
-        <v>245</v>
-      </c>
-      <c r="G30" t="s">
-        <v>144</v>
-      </c>
-      <c r="H30">
-        <v>6500000</v>
-      </c>
-      <c r="I30" t="s">
-        <v>145</v>
-      </c>
-      <c r="J30" t="s">
-        <v>146</v>
-      </c>
-      <c r="K30" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
-        <v>147</v>
-      </c>
-      <c r="B31" t="s">
-        <v>142</v>
-      </c>
-      <c r="C31" t="s">
-        <v>148</v>
-      </c>
-      <c r="D31">
-        <v>4</v>
-      </c>
-      <c r="E31">
-        <v>1</v>
-      </c>
-      <c r="F31">
-        <v>220</v>
-      </c>
-      <c r="G31" t="s">
-        <v>41</v>
-      </c>
-      <c r="H31">
-        <v>4000000</v>
-      </c>
-      <c r="I31" t="s">
-        <v>149</v>
-      </c>
-      <c r="J31" t="s">
-        <v>150</v>
-      </c>
-      <c r="K31" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
-        <v>151</v>
-      </c>
-      <c r="B32" t="s">
-        <v>142</v>
-      </c>
-      <c r="C32" t="s">
-        <v>152</v>
-      </c>
-      <c r="D32">
-        <v>3</v>
-      </c>
-      <c r="E32">
-        <v>3</v>
-      </c>
-      <c r="F32">
-        <v>175</v>
-      </c>
-      <c r="G32" t="s">
-        <v>41</v>
-      </c>
-      <c r="H32">
-        <v>10000000</v>
-      </c>
-      <c r="I32" t="s">
-        <v>129</v>
-      </c>
-      <c r="J32" t="s">
-        <v>153</v>
-      </c>
-      <c r="K32" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
-        <v>154</v>
-      </c>
-      <c r="B33" t="s">
-        <v>142</v>
-      </c>
-      <c r="C33" t="s">
-        <v>89</v>
-      </c>
-      <c r="D33">
-        <v>4</v>
-      </c>
-      <c r="E33">
-        <v>2</v>
-      </c>
-      <c r="F33">
-        <v>205</v>
-      </c>
-      <c r="G33" t="s">
-        <v>41</v>
-      </c>
-      <c r="H33">
-        <v>8000000</v>
-      </c>
-      <c r="I33" t="s">
-        <v>155</v>
-      </c>
-      <c r="J33" t="s">
-        <v>156</v>
-      </c>
-      <c r="K33" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
-        <v>157</v>
-      </c>
-      <c r="B34" t="s">
-        <v>142</v>
-      </c>
-      <c r="C34" t="s">
-        <v>148</v>
-      </c>
-      <c r="D34">
-        <v>3</v>
-      </c>
-      <c r="E34">
-        <v>3</v>
-      </c>
-      <c r="F34">
-        <v>220</v>
-      </c>
-      <c r="G34" t="s">
-        <v>41</v>
-      </c>
-      <c r="H34">
-        <v>8000000</v>
-      </c>
-      <c r="I34" t="s">
-        <v>158</v>
-      </c>
-      <c r="J34" t="s">
-        <v>159</v>
-      </c>
-      <c r="K34" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
-        <v>160</v>
-      </c>
-      <c r="B35" t="s">
-        <v>142</v>
-      </c>
-      <c r="C35" t="s">
-        <v>161</v>
-      </c>
-      <c r="D35">
-        <v>3</v>
-      </c>
-      <c r="E35">
-        <v>2</v>
-      </c>
-      <c r="F35">
-        <v>166</v>
-      </c>
-      <c r="G35" t="s">
-        <v>162</v>
-      </c>
-      <c r="H35">
-        <v>10500000</v>
-      </c>
-      <c r="I35" t="s">
-        <v>163</v>
-      </c>
-      <c r="J35" t="s">
-        <v>164</v>
-      </c>
-      <c r="K35" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
-        <v>165</v>
-      </c>
-      <c r="B36" t="s">
-        <v>166</v>
-      </c>
-      <c r="C36" t="s">
-        <v>167</v>
-      </c>
-      <c r="D36">
-        <v>5</v>
-      </c>
-      <c r="E36">
-        <v>3</v>
-      </c>
-      <c r="F36">
-        <v>300</v>
-      </c>
-      <c r="G36" t="s">
-        <v>14</v>
-      </c>
-      <c r="H36">
-        <v>8000000</v>
-      </c>
-      <c r="I36" t="s">
-        <v>168</v>
-      </c>
-      <c r="J36" t="s">
-        <v>169</v>
-      </c>
-      <c r="K36" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
-        <v>170</v>
-      </c>
-      <c r="B37" t="s">
-        <v>166</v>
-      </c>
-      <c r="C37" t="s">
-        <v>171</v>
-      </c>
-      <c r="D37">
-        <v>3</v>
-      </c>
-      <c r="E37">
-        <v>4</v>
-      </c>
-      <c r="F37">
-        <v>235</v>
-      </c>
-      <c r="G37" t="s">
-        <v>65</v>
-      </c>
-      <c r="H37">
-        <v>9600000</v>
-      </c>
-      <c r="I37" t="s">
-        <v>172</v>
-      </c>
-      <c r="J37" t="s">
-        <v>173</v>
-      </c>
-      <c r="K37" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
-        <v>174</v>
-      </c>
-      <c r="B38" t="s">
-        <v>166</v>
-      </c>
-      <c r="C38" t="s">
-        <v>175</v>
-      </c>
-      <c r="D38">
-        <v>3</v>
-      </c>
-      <c r="E38">
-        <v>3</v>
-      </c>
-      <c r="F38">
-        <v>235</v>
-      </c>
-      <c r="G38" t="s">
-        <v>41</v>
-      </c>
-      <c r="H38">
-        <v>10700000</v>
-      </c>
-      <c r="I38" t="s">
-        <v>172</v>
-      </c>
-      <c r="J38" t="s">
-        <v>176</v>
-      </c>
-      <c r="K38" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
-        <v>177</v>
-      </c>
-      <c r="B39" t="s">
-        <v>166</v>
-      </c>
-      <c r="C39" t="s">
-        <v>178</v>
-      </c>
-      <c r="D39">
-        <v>3</v>
-      </c>
-      <c r="E39">
-        <v>5</v>
-      </c>
-      <c r="F39">
-        <v>282</v>
-      </c>
-      <c r="G39" t="s">
-        <v>41</v>
-      </c>
-      <c r="H39">
-        <v>7163000</v>
-      </c>
-      <c r="I39" t="s">
-        <v>179</v>
-      </c>
-      <c r="J39" t="s">
-        <v>180</v>
-      </c>
-      <c r="K39" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
-        <v>181</v>
-      </c>
-      <c r="B40" t="s">
-        <v>166</v>
-      </c>
-      <c r="C40" t="s">
-        <v>127</v>
-      </c>
-      <c r="D40">
-        <v>3</v>
-      </c>
-      <c r="E40">
-        <v>3</v>
-      </c>
-      <c r="F40">
-        <v>211</v>
-      </c>
-      <c r="G40" t="s">
-        <v>182</v>
-      </c>
-      <c r="H40">
-        <v>13100000</v>
-      </c>
-      <c r="I40" t="s">
-        <v>183</v>
-      </c>
-      <c r="J40" t="s">
-        <v>184</v>
-      </c>
-      <c r="K40" t="s">
-        <v>17</v>
+      <c r="M40" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/apartments.xlsx
+++ b/apartments.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LOQ\Documents\GitHub\Apartment-Recommendation-Chatbot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F9FC2DAE-282F-4F4F-85F4-98D313DF2EC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9522889F-9402-40D3-A08D-CCD8EF7B11D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{637C1A01-FA05-4636-AD4C-D533005E20C1}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="225">
   <si>
     <t>apartment_id</t>
   </si>
@@ -89,9 +89,6 @@
   </si>
   <si>
     <t>AP002</t>
-  </si>
-  <si>
-    <t>studio</t>
   </si>
   <si>
     <t>Palm Hills New Cairo, Fifth Settlement</t>
@@ -1648,16 +1645,16 @@
         <v>22</v>
       </c>
       <c r="B3" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
         <v>15</v>
       </c>
       <c r="D3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" t="s">
         <v>24</v>
-      </c>
-      <c r="E3" t="s">
-        <v>25</v>
       </c>
       <c r="F3">
         <v>1</v>
@@ -1669,16 +1666,16 @@
         <v>70</v>
       </c>
       <c r="I3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J3">
         <v>6000000</v>
       </c>
       <c r="K3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L3" t="s">
         <v>27</v>
-      </c>
-      <c r="L3" t="s">
-        <v>28</v>
       </c>
       <c r="M3" t="s">
         <v>21</v>
@@ -1686,7 +1683,7 @@
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
@@ -1695,10 +1692,10 @@
         <v>15</v>
       </c>
       <c r="D4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E4" t="s">
         <v>30</v>
-      </c>
-      <c r="E4" t="s">
-        <v>31</v>
       </c>
       <c r="F4">
         <v>3</v>
@@ -1710,16 +1707,16 @@
         <v>144</v>
       </c>
       <c r="I4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J4">
         <v>3500000</v>
       </c>
       <c r="K4" t="s">
+        <v>32</v>
+      </c>
+      <c r="L4" t="s">
         <v>33</v>
-      </c>
-      <c r="L4" t="s">
-        <v>34</v>
       </c>
       <c r="M4" t="s">
         <v>21</v>
@@ -1727,19 +1724,19 @@
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
       </c>
       <c r="C5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D5" t="s">
         <v>36</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>37</v>
-      </c>
-      <c r="E5" t="s">
-        <v>38</v>
       </c>
       <c r="F5">
         <v>3</v>
@@ -1751,16 +1748,16 @@
         <v>176</v>
       </c>
       <c r="I5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J5">
         <v>22936160</v>
       </c>
       <c r="K5" t="s">
+        <v>39</v>
+      </c>
+      <c r="L5" t="s">
         <v>40</v>
-      </c>
-      <c r="L5" t="s">
-        <v>41</v>
       </c>
       <c r="M5" t="s">
         <v>21</v>
@@ -1768,19 +1765,19 @@
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B6" t="s">
         <v>14</v>
       </c>
       <c r="C6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D6" t="s">
         <v>43</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>44</v>
-      </c>
-      <c r="E6" t="s">
-        <v>45</v>
       </c>
       <c r="F6">
         <v>3</v>
@@ -1792,16 +1789,16 @@
         <v>147</v>
       </c>
       <c r="I6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J6">
         <v>7500000</v>
       </c>
       <c r="K6" t="s">
+        <v>46</v>
+      </c>
+      <c r="L6" t="s">
         <v>47</v>
-      </c>
-      <c r="L6" t="s">
-        <v>48</v>
       </c>
       <c r="M6" t="s">
         <v>21</v>
@@ -1809,7 +1806,7 @@
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B7" t="s">
         <v>14</v>
@@ -1818,10 +1815,10 @@
         <v>15</v>
       </c>
       <c r="D7" t="s">
+        <v>49</v>
+      </c>
+      <c r="E7" t="s">
         <v>50</v>
-      </c>
-      <c r="E7" t="s">
-        <v>51</v>
       </c>
       <c r="F7">
         <v>3</v>
@@ -1833,16 +1830,16 @@
         <v>186</v>
       </c>
       <c r="I7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J7">
         <v>7500000</v>
       </c>
       <c r="K7" t="s">
+        <v>52</v>
+      </c>
+      <c r="L7" t="s">
         <v>53</v>
-      </c>
-      <c r="L7" t="s">
-        <v>54</v>
       </c>
       <c r="M7" t="s">
         <v>21</v>
@@ -1850,7 +1847,7 @@
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B8" t="s">
         <v>14</v>
@@ -1859,10 +1856,10 @@
         <v>15</v>
       </c>
       <c r="D8" t="s">
+        <v>55</v>
+      </c>
+      <c r="E8" t="s">
         <v>56</v>
-      </c>
-      <c r="E8" t="s">
-        <v>57</v>
       </c>
       <c r="F8">
         <v>2</v>
@@ -1874,16 +1871,16 @@
         <v>101</v>
       </c>
       <c r="I8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J8">
         <v>4000000</v>
       </c>
       <c r="K8" t="s">
+        <v>58</v>
+      </c>
+      <c r="L8" t="s">
         <v>59</v>
-      </c>
-      <c r="L8" t="s">
-        <v>60</v>
       </c>
       <c r="M8" t="s">
         <v>21</v>
@@ -1891,19 +1888,19 @@
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B9" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="C9" t="s">
         <v>15</v>
       </c>
       <c r="D9" t="s">
+        <v>61</v>
+      </c>
+      <c r="E9" t="s">
         <v>62</v>
-      </c>
-      <c r="E9" t="s">
-        <v>63</v>
       </c>
       <c r="F9">
         <v>1</v>
@@ -1915,16 +1912,16 @@
         <v>100</v>
       </c>
       <c r="I9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J9">
         <v>5500000</v>
       </c>
       <c r="K9" t="s">
+        <v>63</v>
+      </c>
+      <c r="L9" t="s">
         <v>64</v>
-      </c>
-      <c r="L9" t="s">
-        <v>65</v>
       </c>
       <c r="M9" t="s">
         <v>21</v>
@@ -1932,7 +1929,7 @@
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B10" t="s">
         <v>14</v>
@@ -1941,10 +1938,10 @@
         <v>15</v>
       </c>
       <c r="D10" t="s">
+        <v>66</v>
+      </c>
+      <c r="E10" t="s">
         <v>67</v>
-      </c>
-      <c r="E10" t="s">
-        <v>68</v>
       </c>
       <c r="F10">
         <v>2</v>
@@ -1956,16 +1953,16 @@
         <v>127</v>
       </c>
       <c r="I10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J10">
         <v>3000000</v>
       </c>
       <c r="K10" t="s">
+        <v>69</v>
+      </c>
+      <c r="L10" t="s">
         <v>70</v>
-      </c>
-      <c r="L10" t="s">
-        <v>71</v>
       </c>
       <c r="M10" t="s">
         <v>21</v>
@@ -1973,19 +1970,19 @@
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B11" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="C11" t="s">
         <v>15</v>
       </c>
       <c r="D11" t="s">
+        <v>72</v>
+      </c>
+      <c r="E11" t="s">
         <v>73</v>
-      </c>
-      <c r="E11" t="s">
-        <v>74</v>
       </c>
       <c r="F11">
         <v>1</v>
@@ -1997,16 +1994,16 @@
         <v>40</v>
       </c>
       <c r="I11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J11">
         <v>2000000</v>
       </c>
       <c r="K11" t="s">
+        <v>75</v>
+      </c>
+      <c r="L11" t="s">
         <v>76</v>
-      </c>
-      <c r="L11" t="s">
-        <v>77</v>
       </c>
       <c r="M11" t="s">
         <v>21</v>
@@ -2014,19 +2011,19 @@
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B12" t="s">
         <v>14</v>
       </c>
       <c r="C12" t="s">
+        <v>78</v>
+      </c>
+      <c r="D12" t="s">
         <v>79</v>
       </c>
-      <c r="D12" t="s">
+      <c r="E12" t="s">
         <v>80</v>
-      </c>
-      <c r="E12" t="s">
-        <v>81</v>
       </c>
       <c r="F12">
         <v>3</v>
@@ -2038,16 +2035,16 @@
         <v>136</v>
       </c>
       <c r="I12" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J12">
         <v>6100000</v>
       </c>
       <c r="K12" t="s">
+        <v>82</v>
+      </c>
+      <c r="L12" t="s">
         <v>83</v>
-      </c>
-      <c r="L12" t="s">
-        <v>84</v>
       </c>
       <c r="M12" t="s">
         <v>21</v>
@@ -2055,19 +2052,19 @@
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B13" t="s">
         <v>14</v>
       </c>
       <c r="C13" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D13" t="s">
+        <v>85</v>
+      </c>
+      <c r="E13" t="s">
         <v>86</v>
-      </c>
-      <c r="E13" t="s">
-        <v>87</v>
       </c>
       <c r="F13">
         <v>3</v>
@@ -2079,16 +2076,16 @@
         <v>154</v>
       </c>
       <c r="I13" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J13">
         <v>5200000</v>
       </c>
       <c r="K13" t="s">
+        <v>88</v>
+      </c>
+      <c r="L13" t="s">
         <v>89</v>
-      </c>
-      <c r="L13" t="s">
-        <v>90</v>
       </c>
       <c r="M13" t="s">
         <v>21</v>
@@ -2096,7 +2093,7 @@
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B14" t="s">
         <v>14</v>
@@ -2105,10 +2102,10 @@
         <v>15</v>
       </c>
       <c r="D14" t="s">
+        <v>91</v>
+      </c>
+      <c r="E14" t="s">
         <v>92</v>
-      </c>
-      <c r="E14" t="s">
-        <v>93</v>
       </c>
       <c r="F14">
         <v>2</v>
@@ -2120,16 +2117,16 @@
         <v>136</v>
       </c>
       <c r="I14" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="J14">
         <v>10700000</v>
       </c>
       <c r="K14" t="s">
+        <v>94</v>
+      </c>
+      <c r="L14" t="s">
         <v>95</v>
-      </c>
-      <c r="L14" t="s">
-        <v>96</v>
       </c>
       <c r="M14" t="s">
         <v>21</v>
@@ -2137,19 +2134,19 @@
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B15" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="C15" t="s">
         <v>15</v>
       </c>
       <c r="D15" t="s">
+        <v>97</v>
+      </c>
+      <c r="E15" t="s">
         <v>98</v>
-      </c>
-      <c r="E15" t="s">
-        <v>99</v>
       </c>
       <c r="F15">
         <v>1</v>
@@ -2161,16 +2158,16 @@
         <v>63</v>
       </c>
       <c r="I15" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="J15">
         <v>3958900</v>
       </c>
       <c r="K15" t="s">
+        <v>100</v>
+      </c>
+      <c r="L15" t="s">
         <v>101</v>
-      </c>
-      <c r="L15" t="s">
-        <v>102</v>
       </c>
       <c r="M15" t="s">
         <v>21</v>
@@ -2178,7 +2175,7 @@
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B16" t="s">
         <v>14</v>
@@ -2187,10 +2184,10 @@
         <v>15</v>
       </c>
       <c r="D16" t="s">
+        <v>103</v>
+      </c>
+      <c r="E16" t="s">
         <v>104</v>
-      </c>
-      <c r="E16" t="s">
-        <v>105</v>
       </c>
       <c r="F16">
         <v>3</v>
@@ -2202,16 +2199,16 @@
         <v>170</v>
       </c>
       <c r="I16" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J16">
         <v>8400000</v>
       </c>
       <c r="K16" t="s">
+        <v>105</v>
+      </c>
+      <c r="L16" t="s">
         <v>106</v>
-      </c>
-      <c r="L16" t="s">
-        <v>107</v>
       </c>
       <c r="M16" t="s">
         <v>21</v>
@@ -2219,19 +2216,19 @@
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
+        <v>107</v>
+      </c>
+      <c r="B17" t="s">
         <v>108</v>
-      </c>
-      <c r="B17" t="s">
-        <v>109</v>
       </c>
       <c r="C17" t="s">
         <v>15</v>
       </c>
       <c r="D17" t="s">
+        <v>109</v>
+      </c>
+      <c r="E17" t="s">
         <v>110</v>
-      </c>
-      <c r="E17" t="s">
-        <v>111</v>
       </c>
       <c r="F17">
         <v>3</v>
@@ -2243,16 +2240,16 @@
         <v>205</v>
       </c>
       <c r="I17" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="J17">
         <v>12500000</v>
       </c>
       <c r="K17" t="s">
+        <v>112</v>
+      </c>
+      <c r="L17" t="s">
         <v>113</v>
-      </c>
-      <c r="L17" t="s">
-        <v>114</v>
       </c>
       <c r="M17" t="s">
         <v>21</v>
@@ -2260,19 +2257,19 @@
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B18" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C18" t="s">
         <v>15</v>
       </c>
       <c r="D18" t="s">
+        <v>115</v>
+      </c>
+      <c r="E18" t="s">
         <v>116</v>
-      </c>
-      <c r="E18" t="s">
-        <v>117</v>
       </c>
       <c r="F18">
         <v>3</v>
@@ -2290,10 +2287,10 @@
         <v>9500000</v>
       </c>
       <c r="K18" t="s">
+        <v>117</v>
+      </c>
+      <c r="L18" t="s">
         <v>118</v>
-      </c>
-      <c r="L18" t="s">
-        <v>119</v>
       </c>
       <c r="M18" t="s">
         <v>21</v>
@@ -2301,19 +2298,19 @@
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B19" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C19" t="s">
         <v>15</v>
       </c>
       <c r="D19" t="s">
+        <v>120</v>
+      </c>
+      <c r="E19" t="s">
         <v>121</v>
-      </c>
-      <c r="E19" t="s">
-        <v>122</v>
       </c>
       <c r="F19">
         <v>0</v>
@@ -2325,16 +2322,16 @@
         <v>199</v>
       </c>
       <c r="I19" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J19">
         <v>18337300</v>
       </c>
       <c r="K19" t="s">
+        <v>122</v>
+      </c>
+      <c r="L19" t="s">
         <v>123</v>
-      </c>
-      <c r="L19" t="s">
-        <v>124</v>
       </c>
       <c r="M19" t="s">
         <v>21</v>
@@ -2342,19 +2339,19 @@
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B20" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C20" t="s">
         <v>15</v>
       </c>
       <c r="D20" t="s">
+        <v>125</v>
+      </c>
+      <c r="E20" t="s">
         <v>126</v>
-      </c>
-      <c r="E20" t="s">
-        <v>127</v>
       </c>
       <c r="F20">
         <v>5</v>
@@ -2366,16 +2363,16 @@
         <v>280</v>
       </c>
       <c r="I20" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J20">
         <v>21500000</v>
       </c>
       <c r="K20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L20" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="M20" t="s">
         <v>21</v>
@@ -2383,19 +2380,19 @@
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B21" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C21" t="s">
         <v>15</v>
       </c>
       <c r="D21" t="s">
+        <v>129</v>
+      </c>
+      <c r="E21" t="s">
         <v>130</v>
-      </c>
-      <c r="E21" t="s">
-        <v>131</v>
       </c>
       <c r="F21">
         <v>3</v>
@@ -2407,16 +2404,16 @@
         <v>166</v>
       </c>
       <c r="I21" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J21">
         <v>10499900</v>
       </c>
       <c r="K21" t="s">
+        <v>131</v>
+      </c>
+      <c r="L21" t="s">
         <v>132</v>
-      </c>
-      <c r="L21" t="s">
-        <v>133</v>
       </c>
       <c r="M21" t="s">
         <v>21</v>
@@ -2424,19 +2421,19 @@
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B22" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C22" t="s">
         <v>15</v>
       </c>
       <c r="D22" t="s">
+        <v>134</v>
+      </c>
+      <c r="E22" t="s">
         <v>135</v>
-      </c>
-      <c r="E22" t="s">
-        <v>136</v>
       </c>
       <c r="F22">
         <v>3</v>
@@ -2448,16 +2445,16 @@
         <v>253</v>
       </c>
       <c r="I22" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="J22">
         <v>16400000</v>
       </c>
       <c r="K22" t="s">
+        <v>137</v>
+      </c>
+      <c r="L22" t="s">
         <v>138</v>
-      </c>
-      <c r="L22" t="s">
-        <v>139</v>
       </c>
       <c r="M22" t="s">
         <v>21</v>
@@ -2465,19 +2462,19 @@
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B23" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C23" t="s">
         <v>15</v>
       </c>
       <c r="D23" t="s">
+        <v>140</v>
+      </c>
+      <c r="E23" t="s">
         <v>141</v>
-      </c>
-      <c r="E23" t="s">
-        <v>142</v>
       </c>
       <c r="F23">
         <v>5</v>
@@ -2489,16 +2486,16 @@
         <v>180</v>
       </c>
       <c r="I23" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="J23">
         <v>10200000</v>
       </c>
       <c r="K23" t="s">
+        <v>143</v>
+      </c>
+      <c r="L23" t="s">
         <v>144</v>
-      </c>
-      <c r="L23" t="s">
-        <v>145</v>
       </c>
       <c r="M23" t="s">
         <v>21</v>
@@ -2506,19 +2503,19 @@
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
+        <v>145</v>
+      </c>
+      <c r="B24" t="s">
+        <v>108</v>
+      </c>
+      <c r="C24" t="s">
+        <v>78</v>
+      </c>
+      <c r="D24" t="s">
         <v>146</v>
       </c>
-      <c r="B24" t="s">
-        <v>109</v>
-      </c>
-      <c r="C24" t="s">
-        <v>79</v>
-      </c>
-      <c r="D24" t="s">
+      <c r="E24" t="s">
         <v>147</v>
-      </c>
-      <c r="E24" t="s">
-        <v>148</v>
       </c>
       <c r="F24">
         <v>4</v>
@@ -2530,16 +2527,16 @@
         <v>392</v>
       </c>
       <c r="I24" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="J24">
         <v>15717417</v>
       </c>
       <c r="K24" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L24" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="M24" t="s">
         <v>21</v>
@@ -2547,19 +2544,19 @@
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B25" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C25" t="s">
         <v>15</v>
       </c>
       <c r="D25" t="s">
+        <v>151</v>
+      </c>
+      <c r="E25" t="s">
         <v>152</v>
-      </c>
-      <c r="E25" t="s">
-        <v>153</v>
       </c>
       <c r="F25">
         <v>5</v>
@@ -2571,16 +2568,16 @@
         <v>225</v>
       </c>
       <c r="I25" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J25">
         <v>15000000</v>
       </c>
       <c r="K25" t="s">
+        <v>153</v>
+      </c>
+      <c r="L25" t="s">
         <v>154</v>
-      </c>
-      <c r="L25" t="s">
-        <v>155</v>
       </c>
       <c r="M25" t="s">
         <v>21</v>
@@ -2588,19 +2585,19 @@
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B26" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C26" t="s">
         <v>15</v>
       </c>
       <c r="D26" t="s">
+        <v>156</v>
+      </c>
+      <c r="E26" t="s">
         <v>157</v>
-      </c>
-      <c r="E26" t="s">
-        <v>158</v>
       </c>
       <c r="F26">
         <v>3</v>
@@ -2612,16 +2609,16 @@
         <v>209</v>
       </c>
       <c r="I26" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="J26">
         <v>14800000</v>
       </c>
       <c r="K26" t="s">
+        <v>159</v>
+      </c>
+      <c r="L26" t="s">
         <v>160</v>
-      </c>
-      <c r="L26" t="s">
-        <v>161</v>
       </c>
       <c r="M26" t="s">
         <v>21</v>
@@ -2629,19 +2626,19 @@
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B27" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C27" t="s">
         <v>15</v>
       </c>
       <c r="D27" t="s">
+        <v>162</v>
+      </c>
+      <c r="E27" t="s">
         <v>163</v>
-      </c>
-      <c r="E27" t="s">
-        <v>164</v>
       </c>
       <c r="F27">
         <v>3</v>
@@ -2659,10 +2656,10 @@
         <v>27000000</v>
       </c>
       <c r="K27" t="s">
+        <v>164</v>
+      </c>
+      <c r="L27" t="s">
         <v>165</v>
-      </c>
-      <c r="L27" t="s">
-        <v>166</v>
       </c>
       <c r="M27" t="s">
         <v>21</v>
@@ -2670,19 +2667,19 @@
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B28" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C28" t="s">
         <v>15</v>
       </c>
       <c r="D28" t="s">
+        <v>167</v>
+      </c>
+      <c r="E28" t="s">
         <v>168</v>
-      </c>
-      <c r="E28" t="s">
-        <v>169</v>
       </c>
       <c r="F28">
         <v>4</v>
@@ -2694,16 +2691,16 @@
         <v>260</v>
       </c>
       <c r="I28" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J28">
         <v>14500000</v>
       </c>
       <c r="K28" t="s">
+        <v>169</v>
+      </c>
+      <c r="L28" t="s">
         <v>170</v>
-      </c>
-      <c r="L28" t="s">
-        <v>171</v>
       </c>
       <c r="M28" t="s">
         <v>21</v>
@@ -2711,19 +2708,19 @@
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B29" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C29" t="s">
         <v>15</v>
       </c>
       <c r="D29" t="s">
+        <v>156</v>
+      </c>
+      <c r="E29" t="s">
         <v>157</v>
-      </c>
-      <c r="E29" t="s">
-        <v>158</v>
       </c>
       <c r="F29">
         <v>4</v>
@@ -2741,10 +2738,10 @@
         <v>12300000</v>
       </c>
       <c r="K29" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="L29" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="M29" t="s">
         <v>21</v>
@@ -2752,19 +2749,19 @@
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
+        <v>173</v>
+      </c>
+      <c r="B30" t="s">
         <v>174</v>
-      </c>
-      <c r="B30" t="s">
-        <v>175</v>
       </c>
       <c r="C30" t="s">
         <v>15</v>
       </c>
       <c r="D30" t="s">
+        <v>175</v>
+      </c>
+      <c r="E30" t="s">
         <v>176</v>
-      </c>
-      <c r="E30" t="s">
-        <v>177</v>
       </c>
       <c r="F30">
         <v>4</v>
@@ -2776,16 +2773,16 @@
         <v>245</v>
       </c>
       <c r="I30" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="J30">
         <v>6500000</v>
       </c>
       <c r="K30" t="s">
+        <v>178</v>
+      </c>
+      <c r="L30" t="s">
         <v>179</v>
-      </c>
-      <c r="L30" t="s">
-        <v>180</v>
       </c>
       <c r="M30" t="s">
         <v>21</v>
@@ -2793,19 +2790,19 @@
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B31" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C31" t="s">
         <v>15</v>
       </c>
       <c r="D31" t="s">
+        <v>181</v>
+      </c>
+      <c r="E31" t="s">
         <v>182</v>
-      </c>
-      <c r="E31" t="s">
-        <v>183</v>
       </c>
       <c r="F31">
         <v>4</v>
@@ -2817,16 +2814,16 @@
         <v>220</v>
       </c>
       <c r="I31" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J31">
         <v>4000000</v>
       </c>
       <c r="K31" t="s">
+        <v>183</v>
+      </c>
+      <c r="L31" t="s">
         <v>184</v>
-      </c>
-      <c r="L31" t="s">
-        <v>185</v>
       </c>
       <c r="M31" t="s">
         <v>21</v>
@@ -2834,19 +2831,19 @@
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B32" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C32" t="s">
         <v>15</v>
       </c>
       <c r="D32" t="s">
+        <v>186</v>
+      </c>
+      <c r="E32" t="s">
         <v>187</v>
-      </c>
-      <c r="E32" t="s">
-        <v>188</v>
       </c>
       <c r="F32">
         <v>3</v>
@@ -2858,16 +2855,16 @@
         <v>175</v>
       </c>
       <c r="I32" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J32">
         <v>10000000</v>
       </c>
       <c r="K32" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="L32" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="M32" t="s">
         <v>21</v>
@@ -2875,19 +2872,19 @@
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B33" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C33" t="s">
         <v>15</v>
       </c>
       <c r="D33" t="s">
+        <v>109</v>
+      </c>
+      <c r="E33" t="s">
         <v>110</v>
-      </c>
-      <c r="E33" t="s">
-        <v>111</v>
       </c>
       <c r="F33">
         <v>4</v>
@@ -2899,16 +2896,16 @@
         <v>205</v>
       </c>
       <c r="I33" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J33">
         <v>8000000</v>
       </c>
       <c r="K33" t="s">
+        <v>190</v>
+      </c>
+      <c r="L33" t="s">
         <v>191</v>
-      </c>
-      <c r="L33" t="s">
-        <v>192</v>
       </c>
       <c r="M33" t="s">
         <v>21</v>
@@ -2916,19 +2913,19 @@
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B34" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C34" t="s">
         <v>15</v>
       </c>
       <c r="D34" t="s">
+        <v>181</v>
+      </c>
+      <c r="E34" t="s">
         <v>182</v>
-      </c>
-      <c r="E34" t="s">
-        <v>183</v>
       </c>
       <c r="F34">
         <v>3</v>
@@ -2940,16 +2937,16 @@
         <v>220</v>
       </c>
       <c r="I34" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J34">
         <v>8000000</v>
       </c>
       <c r="K34" t="s">
+        <v>193</v>
+      </c>
+      <c r="L34" t="s">
         <v>194</v>
-      </c>
-      <c r="L34" t="s">
-        <v>195</v>
       </c>
       <c r="M34" t="s">
         <v>21</v>
@@ -2957,19 +2954,19 @@
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B35" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C35" t="s">
         <v>15</v>
       </c>
       <c r="D35" t="s">
+        <v>196</v>
+      </c>
+      <c r="E35" t="s">
         <v>197</v>
-      </c>
-      <c r="E35" t="s">
-        <v>198</v>
       </c>
       <c r="F35">
         <v>3</v>
@@ -2981,16 +2978,16 @@
         <v>166</v>
       </c>
       <c r="I35" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="J35">
         <v>10500000</v>
       </c>
       <c r="K35" t="s">
+        <v>199</v>
+      </c>
+      <c r="L35" t="s">
         <v>200</v>
-      </c>
-      <c r="L35" t="s">
-        <v>201</v>
       </c>
       <c r="M35" t="s">
         <v>21</v>
@@ -2998,19 +2995,19 @@
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
+        <v>201</v>
+      </c>
+      <c r="B36" t="s">
         <v>202</v>
-      </c>
-      <c r="B36" t="s">
-        <v>203</v>
       </c>
       <c r="C36" t="s">
         <v>15</v>
       </c>
       <c r="D36" t="s">
+        <v>203</v>
+      </c>
+      <c r="E36" t="s">
         <v>204</v>
-      </c>
-      <c r="E36" t="s">
-        <v>205</v>
       </c>
       <c r="F36">
         <v>5</v>
@@ -3028,10 +3025,10 @@
         <v>8000000</v>
       </c>
       <c r="K36" t="s">
+        <v>205</v>
+      </c>
+      <c r="L36" t="s">
         <v>206</v>
-      </c>
-      <c r="L36" t="s">
-        <v>207</v>
       </c>
       <c r="M36" t="s">
         <v>21</v>
@@ -3039,19 +3036,19 @@
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B37" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C37" t="s">
         <v>15</v>
       </c>
       <c r="D37" t="s">
+        <v>208</v>
+      </c>
+      <c r="E37" t="s">
         <v>209</v>
-      </c>
-      <c r="E37" t="s">
-        <v>210</v>
       </c>
       <c r="F37">
         <v>3</v>
@@ -3063,16 +3060,16 @@
         <v>235</v>
       </c>
       <c r="I37" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J37">
         <v>9600000</v>
       </c>
       <c r="K37" t="s">
+        <v>210</v>
+      </c>
+      <c r="L37" t="s">
         <v>211</v>
-      </c>
-      <c r="L37" t="s">
-        <v>212</v>
       </c>
       <c r="M37" t="s">
         <v>21</v>
@@ -3080,19 +3077,19 @@
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B38" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C38" t="s">
         <v>15</v>
       </c>
       <c r="D38" t="s">
+        <v>213</v>
+      </c>
+      <c r="E38" t="s">
         <v>214</v>
-      </c>
-      <c r="E38" t="s">
-        <v>215</v>
       </c>
       <c r="F38">
         <v>3</v>
@@ -3104,16 +3101,16 @@
         <v>235</v>
       </c>
       <c r="I38" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J38">
         <v>10700000</v>
       </c>
       <c r="K38" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L38" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="M38" t="s">
         <v>21</v>
@@ -3121,19 +3118,19 @@
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
+        <v>216</v>
+      </c>
+      <c r="B39" t="s">
+        <v>202</v>
+      </c>
+      <c r="C39" t="s">
+        <v>78</v>
+      </c>
+      <c r="D39" t="s">
         <v>217</v>
       </c>
-      <c r="B39" t="s">
-        <v>203</v>
-      </c>
-      <c r="C39" t="s">
-        <v>79</v>
-      </c>
-      <c r="D39" t="s">
+      <c r="E39" t="s">
         <v>218</v>
-      </c>
-      <c r="E39" t="s">
-        <v>219</v>
       </c>
       <c r="F39">
         <v>3</v>
@@ -3145,16 +3142,16 @@
         <v>282</v>
       </c>
       <c r="I39" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J39">
         <v>7163000</v>
       </c>
       <c r="K39" t="s">
+        <v>219</v>
+      </c>
+      <c r="L39" t="s">
         <v>220</v>
-      </c>
-      <c r="L39" t="s">
-        <v>221</v>
       </c>
       <c r="M39" t="s">
         <v>21</v>
@@ -3162,19 +3159,19 @@
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B40" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C40" t="s">
         <v>15</v>
       </c>
       <c r="D40" t="s">
+        <v>156</v>
+      </c>
+      <c r="E40" t="s">
         <v>157</v>
-      </c>
-      <c r="E40" t="s">
-        <v>158</v>
       </c>
       <c r="F40">
         <v>3</v>
@@ -3186,16 +3183,16 @@
         <v>211</v>
       </c>
       <c r="I40" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="J40">
         <v>13100000</v>
       </c>
       <c r="K40" t="s">
+        <v>223</v>
+      </c>
+      <c r="L40" t="s">
         <v>224</v>
-      </c>
-      <c r="L40" t="s">
-        <v>225</v>
       </c>
       <c r="M40" t="s">
         <v>21</v>

--- a/apartments.xlsx
+++ b/apartments.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LOQ\Documents\GitHub\Apartment-Recommendation-Chatbot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_8EF9489653267378438AF94012CA503B7E0A398A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9361FBCF-94D5-4E4E-B0A3-D97432F7E6D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="823" uniqueCount="424">
   <si>
     <t>apartment_id</t>
   </si>
@@ -830,13 +830,475 @@
   </si>
   <si>
     <t>Semi-finished townhouse for sale in Beverly Hills, Sheikh Zayed. The unit offers 220 sqm with 3 bedrooms, 4 bathrooms, a large reception, kitchen, maid room, and private garden in a prime residential compound.</t>
+  </si>
+  <si>
+    <t>Apartment</t>
+  </si>
+  <si>
+    <t>Sheikh Zayed</t>
+  </si>
+  <si>
+    <t>AlKarma Kay</t>
+  </si>
+  <si>
+    <t>AlKarma Kay, Sheikh Zayed</t>
+  </si>
+  <si>
+    <t>Compound View</t>
+  </si>
+  <si>
+    <t>Fully finished, ACs, swimming pools, green spaces, water features, running tracks, cycling tracks, kids area, commercial mall, surveillance cameras, 24/7 security</t>
+  </si>
+  <si>
+    <t>Fully finished 111 sqm apartment with ACs in AlKarma Kay, Sheikh Zayed by Al Karma Developments. Prime location with flexible payment plans up to 8 years.</t>
+  </si>
+  <si>
+    <t>AP020</t>
+  </si>
+  <si>
+    <t>AP021</t>
+  </si>
+  <si>
+    <t>Vye Sodic</t>
+  </si>
+  <si>
+    <t>Vye Sodic, New Zayed</t>
+  </si>
+  <si>
+    <t>Landscape View</t>
+  </si>
+  <si>
+    <t>Fully finished, ready to move, clubhouse, co-working spaces, school, yoga areas, BBQ area, restaurants, cafes, landscape, gym, spa, clinics, jogging tracks, water features, security, CCTV</t>
+  </si>
+  <si>
+    <t>Ready to move fully finished apartment in Vye Sodic, New Zayed. 158 sqm with 3 bedrooms including master, dressing room, nanny room, and landscape view. Located near Belle Vie, The Estates, Six West, and key landmarks with flexible payment plan.</t>
+  </si>
+  <si>
+    <t>AP022</t>
+  </si>
+  <si>
+    <t>Six West</t>
+  </si>
+  <si>
+    <t>Six West, Beverly Hills, Sheikh Zayed</t>
+  </si>
+  <si>
+    <t>Fully finished, furnished, green landscapes, swimming pool, 24/7 security</t>
+  </si>
+  <si>
+    <t>Fully finished and furnished apartment for immediate delivery in Six West, Beverly Hills, Sheikh Zayed. 150 sqm with 3 bedrooms including master with dressing, located near Waslet Dahshur and Arkan Plaza with installment plan up to 6 years.</t>
+  </si>
+  <si>
+    <t>AP023</t>
+  </si>
+  <si>
+    <t>Beverly Hills</t>
+  </si>
+  <si>
+    <t>Garden View</t>
+  </si>
+  <si>
+    <t>Fully finished, green spaces, security, clubhouse</t>
+  </si>
+  <si>
+    <t>Apartment in Beverly Hills with 2 bedrooms and garden view in a premium compound.</t>
+  </si>
+  <si>
+    <t>AP024</t>
+  </si>
+  <si>
+    <t>Fully finished, clubhouse, gym, tracks, security</t>
+  </si>
+  <si>
+    <t>Modern apartment in Vye Sodic with spacious layout and landscape view.</t>
+  </si>
+  <si>
+    <t>AP025</t>
+  </si>
+  <si>
+    <t>ZED West</t>
+  </si>
+  <si>
+    <t>ZED West, Sheikh Zayed</t>
+  </si>
+  <si>
+    <t>City View</t>
+  </si>
+  <si>
+    <t>Fully finished, smart system, security</t>
+  </si>
+  <si>
+    <t>Compact apartment in ZED West with smart systems and city view.</t>
+  </si>
+  <si>
+    <t>AP026</t>
+  </si>
+  <si>
+    <t>Allegria</t>
+  </si>
+  <si>
+    <t>Fully finished, clubhouse, security</t>
+  </si>
+  <si>
+    <t>Apartment in Allegria with modern layout and green views.</t>
+  </si>
+  <si>
+    <t>AP027</t>
+  </si>
+  <si>
+    <t>Fully finished, security, pool</t>
+  </si>
+  <si>
+    <t>Apartment in Six West with balanced layout and premium location.</t>
+  </si>
+  <si>
+    <t>AP028</t>
+  </si>
+  <si>
+    <t>Westown</t>
+  </si>
+  <si>
+    <t>Westown, Sheikh Zayed</t>
+  </si>
+  <si>
+    <t>Apartment in Westown Sodic ideal for small families.</t>
+  </si>
+  <si>
+    <t>AP029</t>
+  </si>
+  <si>
+    <t>Belle Vie</t>
+  </si>
+  <si>
+    <t>Belle Vie, Sheikh Zayed</t>
+  </si>
+  <si>
+    <t>Large apartment in Belle Vie with open landscape view.</t>
+  </si>
+  <si>
+    <t>Townhouse</t>
+  </si>
+  <si>
+    <t>The Estates</t>
+  </si>
+  <si>
+    <t>The Estates, Sheikh Zayed</t>
+  </si>
+  <si>
+    <t>Semi finished, garden, clubhouse, security</t>
+  </si>
+  <si>
+    <t>Townhouse in The Estates with private garden.</t>
+  </si>
+  <si>
+    <t>Fully finished, clubhouse, pools, security</t>
+  </si>
+  <si>
+    <t>Spacious townhouse in Belle Vie ideal for families.</t>
+  </si>
+  <si>
+    <t>Fully finished, garden, clubhouse, security</t>
+  </si>
+  <si>
+    <t>Townhouse in Westown with premium finishing.</t>
+  </si>
+  <si>
+    <t>Townhouse in ZED West with modern design.</t>
+  </si>
+  <si>
+    <t>Fully finished, golf view, security</t>
+  </si>
+  <si>
+    <t>Townhouse overlooking greenery in Allegria.</t>
+  </si>
+  <si>
+    <t>TH018</t>
+  </si>
+  <si>
+    <t>Fully finished, pool, security</t>
+  </si>
+  <si>
+    <t>Townhouse in Six West with prime location.</t>
+  </si>
+  <si>
+    <t>PH007</t>
+  </si>
+  <si>
+    <t>Penthouse</t>
+  </si>
+  <si>
+    <t>Open View</t>
+  </si>
+  <si>
+    <t>Fully finished, terrace, clubhouse, security</t>
+  </si>
+  <si>
+    <t>Penthouse with large terrace and open views.</t>
+  </si>
+  <si>
+    <t>PH008</t>
+  </si>
+  <si>
+    <t>Fully finished, terrace, gym, security</t>
+  </si>
+  <si>
+    <t>Luxury penthouse with panoramic views.</t>
+  </si>
+  <si>
+    <t>PH009</t>
+  </si>
+  <si>
+    <t>Fully finished, terrace, smart system</t>
+  </si>
+  <si>
+    <t>Penthouse in ZED with city skyline view.</t>
+  </si>
+  <si>
+    <t>DP001</t>
+  </si>
+  <si>
+    <t>Duplex</t>
+  </si>
+  <si>
+    <t>Fully finished, garden access, security</t>
+  </si>
+  <si>
+    <t>Duplex in Six West with garden access.</t>
+  </si>
+  <si>
+    <t>DP002</t>
+  </si>
+  <si>
+    <t>Fully finished, ACs, clubhouse, security</t>
+  </si>
+  <si>
+    <t>Duplex in AlKarma Kay with large spaces.</t>
+  </si>
+  <si>
+    <t>DP003</t>
+  </si>
+  <si>
+    <t>Fully finished, garden, clubhouse</t>
+  </si>
+  <si>
+    <t>Duplex in Belle Vie with modern layout.</t>
+  </si>
+  <si>
+    <t>DP004</t>
+  </si>
+  <si>
+    <t>Semi finished, clubhouse, security</t>
+  </si>
+  <si>
+    <t>Spacious duplex in The Estates compound.</t>
+  </si>
+  <si>
+    <t>AP030</t>
+  </si>
+  <si>
+    <t>October</t>
+  </si>
+  <si>
+    <t>Palm Hills</t>
+  </si>
+  <si>
+    <t>Palm Hills, October</t>
+  </si>
+  <si>
+    <t>Fully finished, clubhouse, security, green spaces</t>
+  </si>
+  <si>
+    <t>Apartment in Palm Hills October with garden view and modern finishing.</t>
+  </si>
+  <si>
+    <t>AP031</t>
+  </si>
+  <si>
+    <t>Mountain View iCity</t>
+  </si>
+  <si>
+    <t>Mountain View iCity, October</t>
+  </si>
+  <si>
+    <t>Lagoon View</t>
+  </si>
+  <si>
+    <t>Fully finished, lagoons, clubhouse, security</t>
+  </si>
+  <si>
+    <t>Apartment in MV iCity with lagoon view and family-friendly layout.</t>
+  </si>
+  <si>
+    <t>AP032</t>
+  </si>
+  <si>
+    <t>Badya</t>
+  </si>
+  <si>
+    <t>Fully finished, smart system, clubhouse, security</t>
+  </si>
+  <si>
+    <t>Modern apartment in Badya with smart features and prime location.</t>
+  </si>
+  <si>
+    <t>AP033</t>
+  </si>
+  <si>
+    <t>O West</t>
+  </si>
+  <si>
+    <t>O West, October</t>
+  </si>
+  <si>
+    <t>Fully finished, clubhouse, gym, security</t>
+  </si>
+  <si>
+    <t>Apartment in O West with green views and modern design.</t>
+  </si>
+  <si>
+    <t>AP034</t>
+  </si>
+  <si>
+    <t>Sun Capital</t>
+  </si>
+  <si>
+    <t>Sun Capital, October</t>
+  </si>
+  <si>
+    <t>Pyramid View</t>
+  </si>
+  <si>
+    <t>Fully finished, security, commercial area</t>
+  </si>
+  <si>
+    <t>Apartment near the pyramids in Sun Capital with open views.</t>
+  </si>
+  <si>
+    <t>AP035</t>
+  </si>
+  <si>
+    <t>October Plaza</t>
+  </si>
+  <si>
+    <t>October Plaza, October</t>
+  </si>
+  <si>
+    <t>Pool View</t>
+  </si>
+  <si>
+    <t>Fully finished, pools, clubhouse, security</t>
+  </si>
+  <si>
+    <t>Apartment in October Plaza with pool view and prime location.</t>
+  </si>
+  <si>
+    <t>AP036</t>
+  </si>
+  <si>
+    <t>AEON Towers</t>
+  </si>
+  <si>
+    <t>AEON Towers, October</t>
+  </si>
+  <si>
+    <t>Fully finished, high-rise, security</t>
+  </si>
+  <si>
+    <t>Apartment in AEON Towers with panoramic city views.</t>
+  </si>
+  <si>
+    <t>TH019</t>
+  </si>
+  <si>
+    <t>Townhouse in Palm Hills with private garden.</t>
+  </si>
+  <si>
+    <t>TH020</t>
+  </si>
+  <si>
+    <t>Townhouse in MV iCity with lagoon-facing unit.</t>
+  </si>
+  <si>
+    <t>TH021</t>
+  </si>
+  <si>
+    <t>Townhouse in O West with modern design and garden.</t>
+  </si>
+  <si>
+    <t>TH022</t>
+  </si>
+  <si>
+    <t>Townhouse in Badya with spacious layout.</t>
+  </si>
+  <si>
+    <t>TH023</t>
+  </si>
+  <si>
+    <t>Townhouse in Sun Capital with competitive price.</t>
+  </si>
+  <si>
+    <t>TH024</t>
+  </si>
+  <si>
+    <t>Fully finished, security, green spaces</t>
+  </si>
+  <si>
+    <t>Townhouse in October Plaza ideal for families.</t>
+  </si>
+  <si>
+    <t>PH010</t>
+  </si>
+  <si>
+    <t>Penthouse in O West with spacious terrace and open view.</t>
+  </si>
+  <si>
+    <t>PH011</t>
+  </si>
+  <si>
+    <t>Fully finished, terrace, lagoons, security</t>
+  </si>
+  <si>
+    <t>Penthouse in MV iCity with premium lagoon view.</t>
+  </si>
+  <si>
+    <t>PH012</t>
+  </si>
+  <si>
+    <t>Penthouse in Palm Hills with garden surroundings.</t>
+  </si>
+  <si>
+    <t>DP005</t>
+  </si>
+  <si>
+    <t>Duplex in Badya with modern finishing and layout.</t>
+  </si>
+  <si>
+    <t>DP006</t>
+  </si>
+  <si>
+    <t>Duplex in O West with large living areas.</t>
+  </si>
+  <si>
+    <t>DP007</t>
+  </si>
+  <si>
+    <t>Duplex in Palm Hills with private garden access.</t>
+  </si>
+  <si>
+    <t>DP008</t>
+  </si>
+  <si>
+    <t>Fully finished, lagoons, security</t>
+  </si>
+  <si>
+    <t>Duplex in MV iCity with premium lagoon-facing unit.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -967,6 +1429,14 @@
     <font>
       <sz val="11"/>
       <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1269,7 +1739,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="42">
+  <cellStyleXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1"/>
@@ -1312,11 +1782,13 @@
     <xf numFmtId="0" fontId="1" fillId="30" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="42"/>
   </cellXfs>
-  <cellStyles count="42">
+  <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="19" xr:uid="{00000000-0005-0000-0000-000013000000}"/>
     <cellStyle name="20% - Accent2" xfId="23" xr:uid="{00000000-0005-0000-0000-000017000000}"/>
     <cellStyle name="20% - Accent3" xfId="27" xr:uid="{00000000-0005-0000-0000-00001B000000}"/>
@@ -1350,6 +1822,7 @@
     <cellStyle name="Heading 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
     <cellStyle name="Heading 3" xfId="4" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
     <cellStyle name="Heading 4" xfId="5" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
+    <cellStyle name="Hyperlink" xfId="42" builtinId="8"/>
     <cellStyle name="Input" xfId="9" xr:uid="{00000000-0005-0000-0000-000009000000}"/>
     <cellStyle name="Linked Cell" xfId="12" xr:uid="{00000000-0005-0000-0000-00000C000000}"/>
     <cellStyle name="Neutral" xfId="8" xr:uid="{00000000-0005-0000-0000-000008000000}"/>
@@ -1522,8 +1995,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M48"/>
+  <dimension ref="A1:M91"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="12" max="12" width="23.5546875" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
@@ -3493,7 +3969,1775 @@
         <v>21</v>
       </c>
     </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>277</v>
+      </c>
+      <c r="B49" t="s">
+        <v>270</v>
+      </c>
+      <c r="C49" t="s">
+        <v>271</v>
+      </c>
+      <c r="D49" t="s">
+        <v>272</v>
+      </c>
+      <c r="E49" t="s">
+        <v>273</v>
+      </c>
+      <c r="F49">
+        <v>2</v>
+      </c>
+      <c r="G49">
+        <v>2</v>
+      </c>
+      <c r="H49">
+        <v>111</v>
+      </c>
+      <c r="I49" t="s">
+        <v>274</v>
+      </c>
+      <c r="J49">
+        <v>1555000</v>
+      </c>
+      <c r="K49" t="s">
+        <v>275</v>
+      </c>
+      <c r="L49" t="s">
+        <v>276</v>
+      </c>
+      <c r="M49" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>278</v>
+      </c>
+      <c r="B50" t="s">
+        <v>270</v>
+      </c>
+      <c r="C50" t="s">
+        <v>271</v>
+      </c>
+      <c r="D50" t="s">
+        <v>279</v>
+      </c>
+      <c r="E50" t="s">
+        <v>280</v>
+      </c>
+      <c r="F50">
+        <v>3</v>
+      </c>
+      <c r="G50">
+        <v>3</v>
+      </c>
+      <c r="H50">
+        <v>158</v>
+      </c>
+      <c r="I50" t="s">
+        <v>281</v>
+      </c>
+      <c r="J50">
+        <v>3960000</v>
+      </c>
+      <c r="K50" t="s">
+        <v>282</v>
+      </c>
+      <c r="L50" t="s">
+        <v>283</v>
+      </c>
+      <c r="M50" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>284</v>
+      </c>
+      <c r="B51" t="s">
+        <v>270</v>
+      </c>
+      <c r="C51" t="s">
+        <v>271</v>
+      </c>
+      <c r="D51" t="s">
+        <v>285</v>
+      </c>
+      <c r="E51" t="s">
+        <v>286</v>
+      </c>
+      <c r="F51">
+        <v>3</v>
+      </c>
+      <c r="G51">
+        <v>2</v>
+      </c>
+      <c r="H51">
+        <v>150</v>
+      </c>
+      <c r="I51" t="s">
+        <v>274</v>
+      </c>
+      <c r="J51">
+        <v>5000000</v>
+      </c>
+      <c r="K51" t="s">
+        <v>287</v>
+      </c>
+      <c r="L51" t="s">
+        <v>288</v>
+      </c>
+      <c r="M51" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>289</v>
+      </c>
+      <c r="B52" t="s">
+        <v>270</v>
+      </c>
+      <c r="C52" t="s">
+        <v>271</v>
+      </c>
+      <c r="D52" t="s">
+        <v>290</v>
+      </c>
+      <c r="E52" t="s">
+        <v>267</v>
+      </c>
+      <c r="F52">
+        <v>2</v>
+      </c>
+      <c r="G52">
+        <v>2</v>
+      </c>
+      <c r="H52">
+        <v>120</v>
+      </c>
+      <c r="I52" t="s">
+        <v>291</v>
+      </c>
+      <c r="J52">
+        <v>3200000</v>
+      </c>
+      <c r="K52" t="s">
+        <v>292</v>
+      </c>
+      <c r="L52" t="s">
+        <v>293</v>
+      </c>
+      <c r="M52" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>294</v>
+      </c>
+      <c r="B53" t="s">
+        <v>270</v>
+      </c>
+      <c r="C53" t="s">
+        <v>271</v>
+      </c>
+      <c r="D53" t="s">
+        <v>279</v>
+      </c>
+      <c r="E53" t="s">
+        <v>280</v>
+      </c>
+      <c r="F53">
+        <v>3</v>
+      </c>
+      <c r="G53">
+        <v>3</v>
+      </c>
+      <c r="H53">
+        <v>165</v>
+      </c>
+      <c r="I53" t="s">
+        <v>281</v>
+      </c>
+      <c r="J53">
+        <v>4200000</v>
+      </c>
+      <c r="K53" t="s">
+        <v>295</v>
+      </c>
+      <c r="L53" t="s">
+        <v>296</v>
+      </c>
+      <c r="M53" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>297</v>
+      </c>
+      <c r="B54" t="s">
+        <v>270</v>
+      </c>
+      <c r="C54" t="s">
+        <v>271</v>
+      </c>
+      <c r="D54" t="s">
+        <v>298</v>
+      </c>
+      <c r="E54" t="s">
+        <v>299</v>
+      </c>
+      <c r="F54">
+        <v>2</v>
+      </c>
+      <c r="G54">
+        <v>1</v>
+      </c>
+      <c r="H54">
+        <v>100</v>
+      </c>
+      <c r="I54" t="s">
+        <v>300</v>
+      </c>
+      <c r="J54">
+        <v>2800000</v>
+      </c>
+      <c r="K54" t="s">
+        <v>301</v>
+      </c>
+      <c r="L54" t="s">
+        <v>302</v>
+      </c>
+      <c r="M54" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>303</v>
+      </c>
+      <c r="B55" t="s">
+        <v>270</v>
+      </c>
+      <c r="C55" t="s">
+        <v>271</v>
+      </c>
+      <c r="D55" t="s">
+        <v>304</v>
+      </c>
+      <c r="E55" t="s">
+        <v>261</v>
+      </c>
+      <c r="F55">
+        <v>3</v>
+      </c>
+      <c r="G55">
+        <v>2</v>
+      </c>
+      <c r="H55">
+        <v>140</v>
+      </c>
+      <c r="I55" t="s">
+        <v>291</v>
+      </c>
+      <c r="J55">
+        <v>3600000</v>
+      </c>
+      <c r="K55" t="s">
+        <v>305</v>
+      </c>
+      <c r="L55" t="s">
+        <v>306</v>
+      </c>
+      <c r="M55" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>307</v>
+      </c>
+      <c r="B56" t="s">
+        <v>270</v>
+      </c>
+      <c r="C56" t="s">
+        <v>271</v>
+      </c>
+      <c r="D56" t="s">
+        <v>285</v>
+      </c>
+      <c r="E56" t="s">
+        <v>286</v>
+      </c>
+      <c r="F56">
+        <v>3</v>
+      </c>
+      <c r="G56">
+        <v>3</v>
+      </c>
+      <c r="H56">
+        <v>155</v>
+      </c>
+      <c r="I56" t="s">
+        <v>274</v>
+      </c>
+      <c r="J56">
+        <v>3900000</v>
+      </c>
+      <c r="K56" t="s">
+        <v>308</v>
+      </c>
+      <c r="L56" t="s">
+        <v>309</v>
+      </c>
+      <c r="M56" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>310</v>
+      </c>
+      <c r="B57" t="s">
+        <v>270</v>
+      </c>
+      <c r="C57" t="s">
+        <v>271</v>
+      </c>
+      <c r="D57" t="s">
+        <v>311</v>
+      </c>
+      <c r="E57" t="s">
+        <v>312</v>
+      </c>
+      <c r="F57">
+        <v>2</v>
+      </c>
+      <c r="G57">
+        <v>2</v>
+      </c>
+      <c r="H57">
+        <v>115</v>
+      </c>
+      <c r="I57" t="s">
+        <v>291</v>
+      </c>
+      <c r="J57">
+        <v>3100000</v>
+      </c>
+      <c r="K57" t="s">
+        <v>305</v>
+      </c>
+      <c r="L57" t="s">
+        <v>313</v>
+      </c>
+      <c r="M57" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>314</v>
+      </c>
+      <c r="B58" t="s">
+        <v>270</v>
+      </c>
+      <c r="C58" t="s">
+        <v>271</v>
+      </c>
+      <c r="D58" t="s">
+        <v>315</v>
+      </c>
+      <c r="E58" t="s">
+        <v>316</v>
+      </c>
+      <c r="F58">
+        <v>3</v>
+      </c>
+      <c r="G58">
+        <v>3</v>
+      </c>
+      <c r="H58">
+        <v>170</v>
+      </c>
+      <c r="I58" t="s">
+        <v>281</v>
+      </c>
+      <c r="J58">
+        <v>4500000</v>
+      </c>
+      <c r="K58" t="s">
+        <v>305</v>
+      </c>
+      <c r="L58" t="s">
+        <v>317</v>
+      </c>
+      <c r="M58" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>171</v>
+      </c>
+      <c r="B59" t="s">
+        <v>318</v>
+      </c>
+      <c r="C59" t="s">
+        <v>271</v>
+      </c>
+      <c r="D59" t="s">
+        <v>319</v>
+      </c>
+      <c r="E59" t="s">
+        <v>320</v>
+      </c>
+      <c r="F59">
+        <v>3</v>
+      </c>
+      <c r="G59">
+        <v>3</v>
+      </c>
+      <c r="H59">
+        <v>220</v>
+      </c>
+      <c r="I59" t="s">
+        <v>291</v>
+      </c>
+      <c r="J59">
+        <v>6500000</v>
+      </c>
+      <c r="K59" t="s">
+        <v>321</v>
+      </c>
+      <c r="L59" t="s">
+        <v>322</v>
+      </c>
+      <c r="M59" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>249</v>
+      </c>
+      <c r="B60" t="s">
+        <v>318</v>
+      </c>
+      <c r="C60" t="s">
+        <v>271</v>
+      </c>
+      <c r="D60" t="s">
+        <v>315</v>
+      </c>
+      <c r="E60" t="s">
+        <v>316</v>
+      </c>
+      <c r="F60">
+        <v>4</v>
+      </c>
+      <c r="G60">
+        <v>4</v>
+      </c>
+      <c r="H60">
+        <v>260</v>
+      </c>
+      <c r="I60" t="s">
+        <v>291</v>
+      </c>
+      <c r="J60">
+        <v>7800000</v>
+      </c>
+      <c r="K60" t="s">
+        <v>323</v>
+      </c>
+      <c r="L60" t="s">
+        <v>324</v>
+      </c>
+      <c r="M60" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>254</v>
+      </c>
+      <c r="B61" t="s">
+        <v>318</v>
+      </c>
+      <c r="C61" t="s">
+        <v>271</v>
+      </c>
+      <c r="D61" t="s">
+        <v>311</v>
+      </c>
+      <c r="E61" t="s">
+        <v>312</v>
+      </c>
+      <c r="F61">
+        <v>3</v>
+      </c>
+      <c r="G61">
+        <v>4</v>
+      </c>
+      <c r="H61">
+        <v>230</v>
+      </c>
+      <c r="I61" t="s">
+        <v>291</v>
+      </c>
+      <c r="J61">
+        <v>7000000</v>
+      </c>
+      <c r="K61" t="s">
+        <v>325</v>
+      </c>
+      <c r="L61" t="s">
+        <v>326</v>
+      </c>
+      <c r="M61" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>259</v>
+      </c>
+      <c r="B62" t="s">
+        <v>318</v>
+      </c>
+      <c r="C62" t="s">
+        <v>271</v>
+      </c>
+      <c r="D62" t="s">
+        <v>298</v>
+      </c>
+      <c r="E62" t="s">
+        <v>299</v>
+      </c>
+      <c r="F62">
+        <v>3</v>
+      </c>
+      <c r="G62">
+        <v>3</v>
+      </c>
+      <c r="H62">
+        <v>210</v>
+      </c>
+      <c r="I62" t="s">
+        <v>274</v>
+      </c>
+      <c r="J62">
+        <v>6200000</v>
+      </c>
+      <c r="K62" t="s">
+        <v>305</v>
+      </c>
+      <c r="L62" t="s">
+        <v>327</v>
+      </c>
+      <c r="M62" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>265</v>
+      </c>
+      <c r="B63" t="s">
+        <v>318</v>
+      </c>
+      <c r="C63" t="s">
+        <v>271</v>
+      </c>
+      <c r="D63" t="s">
+        <v>304</v>
+      </c>
+      <c r="E63" t="s">
+        <v>261</v>
+      </c>
+      <c r="F63">
+        <v>4</v>
+      </c>
+      <c r="G63">
+        <v>4</v>
+      </c>
+      <c r="H63">
+        <v>270</v>
+      </c>
+      <c r="I63" t="s">
+        <v>291</v>
+      </c>
+      <c r="J63">
+        <v>8200000</v>
+      </c>
+      <c r="K63" t="s">
+        <v>328</v>
+      </c>
+      <c r="L63" t="s">
+        <v>329</v>
+      </c>
+      <c r="M63" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>330</v>
+      </c>
+      <c r="B64" t="s">
+        <v>318</v>
+      </c>
+      <c r="C64" t="s">
+        <v>271</v>
+      </c>
+      <c r="D64" t="s">
+        <v>285</v>
+      </c>
+      <c r="E64" t="s">
+        <v>286</v>
+      </c>
+      <c r="F64">
+        <v>3</v>
+      </c>
+      <c r="G64">
+        <v>3</v>
+      </c>
+      <c r="H64">
+        <v>215</v>
+      </c>
+      <c r="I64" t="s">
+        <v>291</v>
+      </c>
+      <c r="J64">
+        <v>6400000</v>
+      </c>
+      <c r="K64" t="s">
+        <v>331</v>
+      </c>
+      <c r="L64" t="s">
+        <v>332</v>
+      </c>
+      <c r="M64" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>333</v>
+      </c>
+      <c r="B65" t="s">
+        <v>334</v>
+      </c>
+      <c r="C65" t="s">
+        <v>271</v>
+      </c>
+      <c r="D65" t="s">
+        <v>304</v>
+      </c>
+      <c r="E65" t="s">
+        <v>261</v>
+      </c>
+      <c r="F65">
+        <v>3</v>
+      </c>
+      <c r="G65">
+        <v>3</v>
+      </c>
+      <c r="H65">
+        <v>200</v>
+      </c>
+      <c r="I65" t="s">
+        <v>335</v>
+      </c>
+      <c r="J65">
+        <v>7200000</v>
+      </c>
+      <c r="K65" t="s">
+        <v>336</v>
+      </c>
+      <c r="L65" t="s">
+        <v>337</v>
+      </c>
+      <c r="M65" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>338</v>
+      </c>
+      <c r="B66" t="s">
+        <v>334</v>
+      </c>
+      <c r="C66" t="s">
+        <v>271</v>
+      </c>
+      <c r="D66" t="s">
+        <v>279</v>
+      </c>
+      <c r="E66" t="s">
+        <v>280</v>
+      </c>
+      <c r="F66">
+        <v>4</v>
+      </c>
+      <c r="G66">
+        <v>4</v>
+      </c>
+      <c r="H66">
+        <v>240</v>
+      </c>
+      <c r="I66" t="s">
+        <v>281</v>
+      </c>
+      <c r="J66">
+        <v>8500000</v>
+      </c>
+      <c r="K66" t="s">
+        <v>339</v>
+      </c>
+      <c r="L66" t="s">
+        <v>340</v>
+      </c>
+      <c r="M66" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>341</v>
+      </c>
+      <c r="B67" t="s">
+        <v>334</v>
+      </c>
+      <c r="C67" t="s">
+        <v>271</v>
+      </c>
+      <c r="D67" t="s">
+        <v>298</v>
+      </c>
+      <c r="E67" t="s">
+        <v>299</v>
+      </c>
+      <c r="F67">
+        <v>3</v>
+      </c>
+      <c r="G67">
+        <v>3</v>
+      </c>
+      <c r="H67">
+        <v>190</v>
+      </c>
+      <c r="I67" t="s">
+        <v>300</v>
+      </c>
+      <c r="J67">
+        <v>6800000</v>
+      </c>
+      <c r="K67" t="s">
+        <v>342</v>
+      </c>
+      <c r="L67" t="s">
+        <v>343</v>
+      </c>
+      <c r="M67" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>344</v>
+      </c>
+      <c r="B68" t="s">
+        <v>345</v>
+      </c>
+      <c r="C68" t="s">
+        <v>271</v>
+      </c>
+      <c r="D68" t="s">
+        <v>285</v>
+      </c>
+      <c r="E68" t="s">
+        <v>286</v>
+      </c>
+      <c r="F68">
+        <v>3</v>
+      </c>
+      <c r="G68">
+        <v>3</v>
+      </c>
+      <c r="H68">
+        <v>210</v>
+      </c>
+      <c r="I68" t="s">
+        <v>291</v>
+      </c>
+      <c r="J68">
+        <v>6100000</v>
+      </c>
+      <c r="K68" t="s">
+        <v>346</v>
+      </c>
+      <c r="L68" t="s">
+        <v>347</v>
+      </c>
+      <c r="M68" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>348</v>
+      </c>
+      <c r="B69" t="s">
+        <v>345</v>
+      </c>
+      <c r="C69" t="s">
+        <v>271</v>
+      </c>
+      <c r="D69" t="s">
+        <v>272</v>
+      </c>
+      <c r="E69" t="s">
+        <v>273</v>
+      </c>
+      <c r="F69">
+        <v>4</v>
+      </c>
+      <c r="G69">
+        <v>4</v>
+      </c>
+      <c r="H69">
+        <v>250</v>
+      </c>
+      <c r="I69" t="s">
+        <v>274</v>
+      </c>
+      <c r="J69">
+        <v>6900000</v>
+      </c>
+      <c r="K69" t="s">
+        <v>349</v>
+      </c>
+      <c r="L69" t="s">
+        <v>350</v>
+      </c>
+      <c r="M69" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="70" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>351</v>
+      </c>
+      <c r="B70" t="s">
+        <v>345</v>
+      </c>
+      <c r="C70" t="s">
+        <v>271</v>
+      </c>
+      <c r="D70" t="s">
+        <v>315</v>
+      </c>
+      <c r="E70" t="s">
+        <v>316</v>
+      </c>
+      <c r="F70">
+        <v>3</v>
+      </c>
+      <c r="G70">
+        <v>3</v>
+      </c>
+      <c r="H70">
+        <v>230</v>
+      </c>
+      <c r="I70" t="s">
+        <v>291</v>
+      </c>
+      <c r="J70">
+        <v>6700000</v>
+      </c>
+      <c r="K70" t="s">
+        <v>352</v>
+      </c>
+      <c r="L70" t="s">
+        <v>353</v>
+      </c>
+      <c r="M70" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="71" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>354</v>
+      </c>
+      <c r="B71" t="s">
+        <v>345</v>
+      </c>
+      <c r="C71" t="s">
+        <v>271</v>
+      </c>
+      <c r="D71" t="s">
+        <v>319</v>
+      </c>
+      <c r="E71" t="s">
+        <v>320</v>
+      </c>
+      <c r="F71">
+        <v>4</v>
+      </c>
+      <c r="G71">
+        <v>4</v>
+      </c>
+      <c r="H71">
+        <v>260</v>
+      </c>
+      <c r="I71" t="s">
+        <v>281</v>
+      </c>
+      <c r="J71">
+        <v>7500000</v>
+      </c>
+      <c r="K71" t="s">
+        <v>355</v>
+      </c>
+      <c r="L71" t="s">
+        <v>356</v>
+      </c>
+      <c r="M71" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="72" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>357</v>
+      </c>
+      <c r="B72" t="s">
+        <v>270</v>
+      </c>
+      <c r="C72" t="s">
+        <v>358</v>
+      </c>
+      <c r="D72" t="s">
+        <v>359</v>
+      </c>
+      <c r="E72" t="s">
+        <v>360</v>
+      </c>
+      <c r="F72">
+        <v>2</v>
+      </c>
+      <c r="G72">
+        <v>2</v>
+      </c>
+      <c r="H72">
+        <v>110</v>
+      </c>
+      <c r="I72" t="s">
+        <v>291</v>
+      </c>
+      <c r="J72">
+        <v>2600000</v>
+      </c>
+      <c r="K72" t="s">
+        <v>361</v>
+      </c>
+      <c r="L72" t="s">
+        <v>362</v>
+      </c>
+      <c r="M72" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="73" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>363</v>
+      </c>
+      <c r="B73" t="s">
+        <v>270</v>
+      </c>
+      <c r="C73" t="s">
+        <v>358</v>
+      </c>
+      <c r="D73" t="s">
+        <v>364</v>
+      </c>
+      <c r="E73" t="s">
+        <v>365</v>
+      </c>
+      <c r="F73">
+        <v>3</v>
+      </c>
+      <c r="G73">
+        <v>2</v>
+      </c>
+      <c r="H73">
+        <v>135</v>
+      </c>
+      <c r="I73" t="s">
+        <v>366</v>
+      </c>
+      <c r="J73">
+        <v>3200000</v>
+      </c>
+      <c r="K73" t="s">
+        <v>367</v>
+      </c>
+      <c r="L73" t="s">
+        <v>368</v>
+      </c>
+      <c r="M73" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="74" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>369</v>
+      </c>
+      <c r="B74" t="s">
+        <v>270</v>
+      </c>
+      <c r="C74" t="s">
+        <v>358</v>
+      </c>
+      <c r="D74" t="s">
+        <v>370</v>
+      </c>
+      <c r="E74" t="s">
+        <v>256</v>
+      </c>
+      <c r="F74">
+        <v>3</v>
+      </c>
+      <c r="G74">
+        <v>3</v>
+      </c>
+      <c r="H74">
+        <v>150</v>
+      </c>
+      <c r="I74" t="s">
+        <v>274</v>
+      </c>
+      <c r="J74">
+        <v>3500000</v>
+      </c>
+      <c r="K74" t="s">
+        <v>371</v>
+      </c>
+      <c r="L74" t="s">
+        <v>372</v>
+      </c>
+      <c r="M74" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="75" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>373</v>
+      </c>
+      <c r="B75" t="s">
+        <v>270</v>
+      </c>
+      <c r="C75" t="s">
+        <v>358</v>
+      </c>
+      <c r="D75" t="s">
+        <v>374</v>
+      </c>
+      <c r="E75" t="s">
+        <v>375</v>
+      </c>
+      <c r="F75">
+        <v>2</v>
+      </c>
+      <c r="G75">
+        <v>2</v>
+      </c>
+      <c r="H75">
+        <v>115</v>
+      </c>
+      <c r="I75" t="s">
+        <v>291</v>
+      </c>
+      <c r="J75">
+        <v>2800000</v>
+      </c>
+      <c r="K75" t="s">
+        <v>376</v>
+      </c>
+      <c r="L75" t="s">
+        <v>377</v>
+      </c>
+      <c r="M75" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="76" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>378</v>
+      </c>
+      <c r="B76" t="s">
+        <v>270</v>
+      </c>
+      <c r="C76" t="s">
+        <v>358</v>
+      </c>
+      <c r="D76" t="s">
+        <v>379</v>
+      </c>
+      <c r="E76" t="s">
+        <v>380</v>
+      </c>
+      <c r="F76">
+        <v>3</v>
+      </c>
+      <c r="G76">
+        <v>2</v>
+      </c>
+      <c r="H76">
+        <v>140</v>
+      </c>
+      <c r="I76" t="s">
+        <v>381</v>
+      </c>
+      <c r="J76">
+        <v>3000000</v>
+      </c>
+      <c r="K76" t="s">
+        <v>382</v>
+      </c>
+      <c r="L76" t="s">
+        <v>383</v>
+      </c>
+      <c r="M76" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="77" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>384</v>
+      </c>
+      <c r="B77" t="s">
+        <v>270</v>
+      </c>
+      <c r="C77" t="s">
+        <v>358</v>
+      </c>
+      <c r="D77" t="s">
+        <v>385</v>
+      </c>
+      <c r="E77" t="s">
+        <v>386</v>
+      </c>
+      <c r="F77">
+        <v>2</v>
+      </c>
+      <c r="G77">
+        <v>1</v>
+      </c>
+      <c r="H77">
+        <v>100</v>
+      </c>
+      <c r="I77" t="s">
+        <v>387</v>
+      </c>
+      <c r="J77">
+        <v>2400000</v>
+      </c>
+      <c r="K77" t="s">
+        <v>388</v>
+      </c>
+      <c r="L77" t="s">
+        <v>389</v>
+      </c>
+      <c r="M77" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="78" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>390</v>
+      </c>
+      <c r="B78" t="s">
+        <v>270</v>
+      </c>
+      <c r="C78" t="s">
+        <v>358</v>
+      </c>
+      <c r="D78" t="s">
+        <v>391</v>
+      </c>
+      <c r="E78" t="s">
+        <v>392</v>
+      </c>
+      <c r="F78">
+        <v>3</v>
+      </c>
+      <c r="G78">
+        <v>3</v>
+      </c>
+      <c r="H78">
+        <v>160</v>
+      </c>
+      <c r="I78" t="s">
+        <v>300</v>
+      </c>
+      <c r="J78">
+        <v>3800000</v>
+      </c>
+      <c r="K78" t="s">
+        <v>393</v>
+      </c>
+      <c r="L78" t="s">
+        <v>394</v>
+      </c>
+      <c r="M78" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="79" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>395</v>
+      </c>
+      <c r="B79" t="s">
+        <v>318</v>
+      </c>
+      <c r="C79" t="s">
+        <v>358</v>
+      </c>
+      <c r="D79" t="s">
+        <v>359</v>
+      </c>
+      <c r="E79" t="s">
+        <v>360</v>
+      </c>
+      <c r="F79">
+        <v>3</v>
+      </c>
+      <c r="G79">
+        <v>3</v>
+      </c>
+      <c r="H79">
+        <v>210</v>
+      </c>
+      <c r="I79" t="s">
+        <v>291</v>
+      </c>
+      <c r="J79">
+        <v>5200000</v>
+      </c>
+      <c r="K79" t="s">
+        <v>321</v>
+      </c>
+      <c r="L79" t="s">
+        <v>396</v>
+      </c>
+      <c r="M79" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="80" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>397</v>
+      </c>
+      <c r="B80" t="s">
+        <v>318</v>
+      </c>
+      <c r="C80" t="s">
+        <v>358</v>
+      </c>
+      <c r="D80" t="s">
+        <v>364</v>
+      </c>
+      <c r="E80" t="s">
+        <v>365</v>
+      </c>
+      <c r="F80">
+        <v>4</v>
+      </c>
+      <c r="G80">
+        <v>4</v>
+      </c>
+      <c r="H80">
+        <v>240</v>
+      </c>
+      <c r="I80" t="s">
+        <v>366</v>
+      </c>
+      <c r="J80">
+        <v>6100000</v>
+      </c>
+      <c r="K80" t="s">
+        <v>367</v>
+      </c>
+      <c r="L80" t="s">
+        <v>398</v>
+      </c>
+      <c r="M80" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="81" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>399</v>
+      </c>
+      <c r="B81" t="s">
+        <v>318</v>
+      </c>
+      <c r="C81" t="s">
+        <v>358</v>
+      </c>
+      <c r="D81" t="s">
+        <v>374</v>
+      </c>
+      <c r="E81" t="s">
+        <v>375</v>
+      </c>
+      <c r="F81">
+        <v>3</v>
+      </c>
+      <c r="G81">
+        <v>4</v>
+      </c>
+      <c r="H81">
+        <v>230</v>
+      </c>
+      <c r="I81" t="s">
+        <v>291</v>
+      </c>
+      <c r="J81">
+        <v>5900000</v>
+      </c>
+      <c r="K81" t="s">
+        <v>305</v>
+      </c>
+      <c r="L81" t="s">
+        <v>400</v>
+      </c>
+      <c r="M81" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="82" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>401</v>
+      </c>
+      <c r="B82" t="s">
+        <v>318</v>
+      </c>
+      <c r="C82" t="s">
+        <v>358</v>
+      </c>
+      <c r="D82" t="s">
+        <v>370</v>
+      </c>
+      <c r="E82" t="s">
+        <v>256</v>
+      </c>
+      <c r="F82">
+        <v>4</v>
+      </c>
+      <c r="G82">
+        <v>4</v>
+      </c>
+      <c r="H82">
+        <v>260</v>
+      </c>
+      <c r="I82" t="s">
+        <v>274</v>
+      </c>
+      <c r="J82">
+        <v>6400000</v>
+      </c>
+      <c r="K82" t="s">
+        <v>301</v>
+      </c>
+      <c r="L82" t="s">
+        <v>402</v>
+      </c>
+      <c r="M82" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="83" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>403</v>
+      </c>
+      <c r="B83" t="s">
+        <v>318</v>
+      </c>
+      <c r="C83" t="s">
+        <v>358</v>
+      </c>
+      <c r="D83" t="s">
+        <v>379</v>
+      </c>
+      <c r="E83" t="s">
+        <v>380</v>
+      </c>
+      <c r="F83">
+        <v>3</v>
+      </c>
+      <c r="G83">
+        <v>3</v>
+      </c>
+      <c r="H83">
+        <v>220</v>
+      </c>
+      <c r="I83" t="s">
+        <v>291</v>
+      </c>
+      <c r="J83">
+        <v>5000000</v>
+      </c>
+      <c r="K83" t="s">
+        <v>355</v>
+      </c>
+      <c r="L83" t="s">
+        <v>404</v>
+      </c>
+      <c r="M83" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="84" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
+        <v>405</v>
+      </c>
+      <c r="B84" t="s">
+        <v>318</v>
+      </c>
+      <c r="C84" t="s">
+        <v>358</v>
+      </c>
+      <c r="D84" t="s">
+        <v>385</v>
+      </c>
+      <c r="E84" t="s">
+        <v>386</v>
+      </c>
+      <c r="F84">
+        <v>3</v>
+      </c>
+      <c r="G84">
+        <v>3</v>
+      </c>
+      <c r="H84">
+        <v>200</v>
+      </c>
+      <c r="I84" t="s">
+        <v>291</v>
+      </c>
+      <c r="J84">
+        <v>4800000</v>
+      </c>
+      <c r="K84" t="s">
+        <v>406</v>
+      </c>
+      <c r="L84" t="s">
+        <v>407</v>
+      </c>
+      <c r="M84" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="85" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
+        <v>408</v>
+      </c>
+      <c r="B85" t="s">
+        <v>334</v>
+      </c>
+      <c r="C85" t="s">
+        <v>358</v>
+      </c>
+      <c r="D85" t="s">
+        <v>374</v>
+      </c>
+      <c r="E85" t="s">
+        <v>375</v>
+      </c>
+      <c r="F85">
+        <v>3</v>
+      </c>
+      <c r="G85">
+        <v>3</v>
+      </c>
+      <c r="H85">
+        <v>190</v>
+      </c>
+      <c r="I85" t="s">
+        <v>335</v>
+      </c>
+      <c r="J85">
+        <v>6000000</v>
+      </c>
+      <c r="K85" t="s">
+        <v>336</v>
+      </c>
+      <c r="L85" t="s">
+        <v>409</v>
+      </c>
+      <c r="M85" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="86" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
+        <v>410</v>
+      </c>
+      <c r="B86" t="s">
+        <v>334</v>
+      </c>
+      <c r="C86" t="s">
+        <v>358</v>
+      </c>
+      <c r="D86" t="s">
+        <v>364</v>
+      </c>
+      <c r="E86" t="s">
+        <v>365</v>
+      </c>
+      <c r="F86">
+        <v>4</v>
+      </c>
+      <c r="G86">
+        <v>4</v>
+      </c>
+      <c r="H86">
+        <v>230</v>
+      </c>
+      <c r="I86" t="s">
+        <v>366</v>
+      </c>
+      <c r="J86">
+        <v>7200000</v>
+      </c>
+      <c r="K86" t="s">
+        <v>411</v>
+      </c>
+      <c r="L86" t="s">
+        <v>412</v>
+      </c>
+      <c r="M86" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="87" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
+        <v>413</v>
+      </c>
+      <c r="B87" t="s">
+        <v>334</v>
+      </c>
+      <c r="C87" t="s">
+        <v>358</v>
+      </c>
+      <c r="D87" t="s">
+        <v>359</v>
+      </c>
+      <c r="E87" t="s">
+        <v>360</v>
+      </c>
+      <c r="F87">
+        <v>3</v>
+      </c>
+      <c r="G87">
+        <v>3</v>
+      </c>
+      <c r="H87">
+        <v>200</v>
+      </c>
+      <c r="I87" t="s">
+        <v>291</v>
+      </c>
+      <c r="J87">
+        <v>6500000</v>
+      </c>
+      <c r="K87" t="s">
+        <v>336</v>
+      </c>
+      <c r="L87" t="s">
+        <v>414</v>
+      </c>
+      <c r="M87" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="88" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
+        <v>415</v>
+      </c>
+      <c r="B88" t="s">
+        <v>345</v>
+      </c>
+      <c r="C88" t="s">
+        <v>358</v>
+      </c>
+      <c r="D88" t="s">
+        <v>370</v>
+      </c>
+      <c r="E88" t="s">
+        <v>256</v>
+      </c>
+      <c r="F88">
+        <v>3</v>
+      </c>
+      <c r="G88">
+        <v>3</v>
+      </c>
+      <c r="H88">
+        <v>210</v>
+      </c>
+      <c r="I88" t="s">
+        <v>291</v>
+      </c>
+      <c r="J88">
+        <v>5500000</v>
+      </c>
+      <c r="K88" t="s">
+        <v>301</v>
+      </c>
+      <c r="L88" t="s">
+        <v>416</v>
+      </c>
+      <c r="M88" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="89" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
+        <v>417</v>
+      </c>
+      <c r="B89" t="s">
+        <v>345</v>
+      </c>
+      <c r="C89" t="s">
+        <v>358</v>
+      </c>
+      <c r="D89" t="s">
+        <v>374</v>
+      </c>
+      <c r="E89" t="s">
+        <v>375</v>
+      </c>
+      <c r="F89">
+        <v>4</v>
+      </c>
+      <c r="G89">
+        <v>4</v>
+      </c>
+      <c r="H89">
+        <v>260</v>
+      </c>
+      <c r="I89" t="s">
+        <v>274</v>
+      </c>
+      <c r="J89">
+        <v>6800000</v>
+      </c>
+      <c r="K89" t="s">
+        <v>305</v>
+      </c>
+      <c r="L89" t="s">
+        <v>418</v>
+      </c>
+      <c r="M89" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="90" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
+        <v>419</v>
+      </c>
+      <c r="B90" t="s">
+        <v>345</v>
+      </c>
+      <c r="C90" t="s">
+        <v>358</v>
+      </c>
+      <c r="D90" t="s">
+        <v>359</v>
+      </c>
+      <c r="E90" t="s">
+        <v>360</v>
+      </c>
+      <c r="F90">
+        <v>3</v>
+      </c>
+      <c r="G90">
+        <v>3</v>
+      </c>
+      <c r="H90">
+        <v>220</v>
+      </c>
+      <c r="I90" t="s">
+        <v>291</v>
+      </c>
+      <c r="J90">
+        <v>5700000</v>
+      </c>
+      <c r="K90" t="s">
+        <v>352</v>
+      </c>
+      <c r="L90" t="s">
+        <v>420</v>
+      </c>
+      <c r="M90" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="91" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
+        <v>421</v>
+      </c>
+      <c r="B91" t="s">
+        <v>345</v>
+      </c>
+      <c r="C91" t="s">
+        <v>358</v>
+      </c>
+      <c r="D91" t="s">
+        <v>364</v>
+      </c>
+      <c r="E91" t="s">
+        <v>365</v>
+      </c>
+      <c r="F91">
+        <v>4</v>
+      </c>
+      <c r="G91">
+        <v>4</v>
+      </c>
+      <c r="H91">
+        <v>270</v>
+      </c>
+      <c r="I91" t="s">
+        <v>366</v>
+      </c>
+      <c r="J91">
+        <v>7500000</v>
+      </c>
+      <c r="K91" t="s">
+        <v>422</v>
+      </c>
+      <c r="L91" t="s">
+        <v>423</v>
+      </c>
+      <c r="M91" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="M51" r:id="rId1" xr:uid="{9A50B3B0-D05F-40DB-B893-E99BF185BA59}"/>
+    <hyperlink ref="M52:M71" r:id="rId2" display="ahmedashraf2452001@gmail.com" xr:uid="{F172BF1B-03FA-4436-9600-7978C2D52A23}"/>
+    <hyperlink ref="M72:M91" r:id="rId3" display="ahmedashraf2452001@gmail.com" xr:uid="{3EC1D6A5-779A-4BB9-8C63-0E2A9F2FFECC}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/apartments.xlsx
+++ b/apartments.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LOQ\Documents\GitHub\Apartment-Recommendation-Chatbot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9361FBCF-94D5-4E4E-B0A3-D97432F7E6D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC9A5ADE-E6E0-403E-B4FC-2F0D17657FCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="823" uniqueCount="424">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="823" uniqueCount="425">
   <si>
     <t>apartment_id</t>
   </si>
@@ -1292,6 +1292,9 @@
   </si>
   <si>
     <t>Duplex in MV iCity with premium lagoon-facing unit.</t>
+  </si>
+  <si>
+    <t>dadakiem2452001@gmail.com</t>
   </si>
 </sst>
 </file>
@@ -2079,8 +2082,8 @@
       <c r="L2" t="s">
         <v>20</v>
       </c>
-      <c r="M2" t="s">
-        <v>21</v>
+      <c r="M2" s="1" t="s">
+        <v>424</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
@@ -5737,6 +5740,7 @@
     <hyperlink ref="M51" r:id="rId1" xr:uid="{9A50B3B0-D05F-40DB-B893-E99BF185BA59}"/>
     <hyperlink ref="M52:M71" r:id="rId2" display="ahmedashraf2452001@gmail.com" xr:uid="{F172BF1B-03FA-4436-9600-7978C2D52A23}"/>
     <hyperlink ref="M72:M91" r:id="rId3" display="ahmedashraf2452001@gmail.com" xr:uid="{3EC1D6A5-779A-4BB9-8C63-0E2A9F2FFECC}"/>
+    <hyperlink ref="M2" r:id="rId4" xr:uid="{3BB6CCD0-2FE0-4336-8EE6-4028F0FE9F8B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/apartments.xlsx
+++ b/apartments.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LOQ\Documents\GitHub\Apartment-Recommendation-Chatbot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC9A5ADE-E6E0-403E-B4FC-2F0D17657FCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B7BE7B1-4378-42FF-8E8B-33BB4E752137}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="823" uniqueCount="425">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="823" uniqueCount="424">
   <si>
     <t>apartment_id</t>
   </si>
@@ -1292,9 +1292,6 @@
   </si>
   <si>
     <t>Duplex in MV iCity with premium lagoon-facing unit.</t>
-  </si>
-  <si>
-    <t>dadakiem2452001@gmail.com</t>
   </si>
 </sst>
 </file>
@@ -2082,8 +2079,8 @@
       <c r="L2" t="s">
         <v>20</v>
       </c>
-      <c r="M2" s="1" t="s">
-        <v>424</v>
+      <c r="M2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
@@ -5740,7 +5737,6 @@
     <hyperlink ref="M51" r:id="rId1" xr:uid="{9A50B3B0-D05F-40DB-B893-E99BF185BA59}"/>
     <hyperlink ref="M52:M71" r:id="rId2" display="ahmedashraf2452001@gmail.com" xr:uid="{F172BF1B-03FA-4436-9600-7978C2D52A23}"/>
     <hyperlink ref="M72:M91" r:id="rId3" display="ahmedashraf2452001@gmail.com" xr:uid="{3EC1D6A5-779A-4BB9-8C63-0E2A9F2FFECC}"/>
-    <hyperlink ref="M2" r:id="rId4" xr:uid="{3BB6CCD0-2FE0-4336-8EE6-4028F0FE9F8B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
